--- a/results/job_matches_2026-06-26.xlsx
+++ b/results/job_matches_2026-06-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Data Engineer (Contract)</t>
+          <t>Engineer/Sr Engineer, IT Data</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ComplexCare Solutions</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a32a20237152630a</t>
+          <t>https://www.indeed.com/viewjob?jk=171509f615b5daa2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Software Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Atlas Group LLC</t>
+          <t>ComplexCare Solutions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96986685e9f66259</t>
+          <t>https://www.indeed.com/viewjob?jk=a32a20237152630a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Manufacturing Intelligence, Machine Learning &amp; AI</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Atlas Group LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wa-Ni Village, TN, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ab95f94071e971b</t>
+          <t>https://www.indeed.com/viewjob?jk=96986685e9f66259</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Architect, Technology I</t>
+          <t>Advisory Associate, AI - Summer 2026 (Houston)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>BDO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mettawa, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, API Gateway, IAM, RDS</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Azure, Data Factory, Databricks</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bde36b833417f68</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5fd57bbd10ca27</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Engineer</t>
+          <t>Senior Data Scientist – Manufacturing Intelligence, Machine Learning &amp; AI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Wa-Ni Village, TN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a074a785ce24052f</t>
+          <t>https://www.indeed.com/viewjob?jk=2ab95f94071e971b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Artificial Intelligence/Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dematic</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,59 +811,59 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9bde3d8a51e4f79</t>
+          <t>https://www.indeed.com/viewjob?jk=a074a785ce24052f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GCP Spanner Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Dematic</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Kafka, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76401a227b65d3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=f9bde3d8a51e4f79</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PLM Teamcenter Solution Architect - Siemens</t>
+          <t>GCP Spanner Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TAN45 TECH</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Kafka, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=747fddb8b55540ea</t>
+          <t>https://www.indeed.com/viewjob?jk=76401a227b65d3e8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Developer, IT Applications</t>
+          <t>PLM Teamcenter Solution Architect - Siemens</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>TAN45 TECH</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, GCP</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d94580e77e2d3def</t>
+          <t>https://www.indeed.com/viewjob?jk=747fddb8b55540ea</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
+          <t>Technology Architect - Product Development</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mindful Support Services</t>
+          <t>Shearwater Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mountlake Terrace, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=650467e40b62799c</t>
+          <t>https://www.indeed.com/viewjob?jk=53d40e3111fd3799</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>Mindful Support Services</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Mountlake Terrace, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Hadoop, Spark, Scala, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0725cc4f521729f5</t>
+          <t>https://www.indeed.com/viewjob?jk=650467e40b62799c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer - Hybrid/Durham,NC</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>Globant</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Hadoop, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85d13cad9b24073</t>
+          <t>https://www.indeed.com/viewjob?jk=0725cc4f521729f5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI</t>
+          <t>Data Solutions Engineer - Hybrid/Durham,NC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0ab478702c96db5</t>
+          <t>https://www.indeed.com/viewjob?jk=f85d13cad9b24073</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DevOps Engineer with Java</t>
+          <t>Senior Data Engineer, AI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91621af2058bcdaf</t>
+          <t>https://www.indeed.com/viewjob?jk=e0ab478702c96db5</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4043bb7b561d2d9</t>
+          <t>https://www.indeed.com/viewjob?jk=91621af2058bcdaf</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GCP Technical Specialist</t>
+          <t>DevOps Engineer with Java</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a829451037364106</t>
+          <t>https://www.indeed.com/viewjob?jk=e4043bb7b561d2d9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Business Intelligence Sr Analyst</t>
+          <t>GCP Technical Specialist</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,69 +1186,69 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Snowflake</t>
+          <t>Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e1d0952eadd1803</t>
+          <t>https://www.indeed.com/viewjob?jk=a829451037364106</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Platform Solutions – Dallas – Associate, Software Engineering – 4208762</t>
+          <t>Business Intelligence Sr Analyst</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, Snowflake, Oracle, Cassandra, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=440eb7ec7c9d835a</t>
+          <t>https://www.indeed.com/viewjob?jk=0e1d0952eadd1803</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer IV</t>
+          <t>Platform Solutions – Dallas – Associate, Software Engineering – 4208762</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vida Health</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, Spark, Scala, Kafka, Snowflake, Oracle, Cassandra, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a816a575de11cfe</t>
+          <t>https://www.indeed.com/viewjob?jk=440eb7ec7c9d835a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Backend Software Engineer IV</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mourant</t>
+          <t>Vida Health</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bba01ebafe36cd2b</t>
+          <t>https://www.indeed.com/viewjob?jk=3a816a575de11cfe</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. AWS Data Architect (Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Mourant</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Hadoop, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=436457a82fb3e61d</t>
+          <t>https://www.indeed.com/viewjob?jk=bba01ebafe36cd2b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - 2373458</t>
+          <t>Senior Java Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, RDS, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff932a257a601c95</t>
+          <t>https://www.indeed.com/viewjob?jk=ec4bd51618d0a580</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LoopNet - Senior Software Engineer</t>
+          <t>Full-Stack Java Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, Kafka, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1582817466d60077</t>
+          <t>https://www.indeed.com/viewjob?jk=651520622efc1265</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer - 2373458</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Splunk, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b16300c5f378062d</t>
+          <t>https://www.indeed.com/viewjob?jk=ff932a257a601c95</t>
         </is>
       </c>
     </row>
@@ -1798,17 +1798,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data &amp; AWS</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>MNTN</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8a9e089237396a3</t>
+          <t>https://www.indeed.com/viewjob?jk=3610cfdfc0364b8e</t>
         </is>
       </c>
     </row>
@@ -1903,17 +1903,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Solutions Architect - Financial Services (Insurance)</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2e4b10d02c9169d</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9a38e235659081</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Financial Services (Wealth and Asset Management)</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8502da83b9f3f55</t>
+          <t>https://www.indeed.com/viewjob?jk=cd0775a42f899524</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Guidewire Integration Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e37631ce8845786</t>
+          <t>https://www.indeed.com/viewjob?jk=b33138f7850dfefc</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Guidewire Integration Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0e4bf24557f7446</t>
+          <t>https://www.indeed.com/viewjob?jk=a342726a84e27f8e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Guidewire Integration Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Clayton, CA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=943f1767bc3da17e</t>
+          <t>https://www.indeed.com/viewjob?jk=c186d8b7ac65fdf8</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Guidewire Integration Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Antioch, CA, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55a3ba405f74d032</t>
+          <t>https://www.indeed.com/viewjob?jk=95cc142f3e2617a6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Guidewire Integration Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Martinez, CA, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53e9315332f2ea0c</t>
+          <t>https://www.indeed.com/viewjob?jk=db16f20add9ea986</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Guidewire Integration Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pleasant Hill, CA, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae88819d628f2aed</t>
+          <t>https://www.indeed.com/viewjob?jk=1382d06b80fb6867</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Guidewire Integration Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48ff3521016f8dd5</t>
+          <t>https://www.indeed.com/viewjob?jk=bcad5c4e643319ff</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Aqua Finance</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Cloud Storage, Scala, Snowflake, Time Travel, clustering keys, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4122f34f0b0a80</t>
+          <t>https://www.indeed.com/viewjob?jk=40e64526422d931b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown Insurance</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f55a36c486ae8573</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d627fd3422104c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Analyst (Data Solutions)</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2ec42f2e29989e</t>
+          <t>https://www.indeed.com/viewjob?jk=fab8211cf6bde1e0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=797e64bcb8624035</t>
+          <t>https://www.indeed.com/viewjob?jk=05bab721c73d545f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eefab3368870cfd6</t>
+          <t>https://www.indeed.com/viewjob?jk=85a706af297ba804</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Clayton, CA, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=992d1d915f9d6362</t>
+          <t>https://www.indeed.com/viewjob?jk=13401bc8d0f3279e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Pleasant Hill, CA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=654b2f67eee1d48c</t>
+          <t>https://www.indeed.com/viewjob?jk=31032458d140d1ae</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=438aec656ad718b9</t>
+          <t>https://www.indeed.com/viewjob?jk=115cfe00112809d8</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f9d760938954181</t>
+          <t>https://www.indeed.com/viewjob?jk=031a5b8865d1f458</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Martinez, CA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6d712eb3900bf51</t>
+          <t>https://www.indeed.com/viewjob?jk=65c6bb88e77fa7e3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. SW Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd564ef34bae6dc8</t>
+          <t>https://www.indeed.com/viewjob?jk=0426526011ecf8ab</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Sonny's Enterprises, Inc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f7c892f9988b1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=e2f4ae59bb2e76db</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93bbd1487e7d0fd7</t>
+          <t>https://www.indeed.com/viewjob?jk=fc596e52195e0933</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29685a938223251</t>
+          <t>https://www.indeed.com/viewjob?jk=44f8b5180e01e140</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a7ce3bbe941f36</t>
+          <t>https://www.indeed.com/viewjob?jk=af0b8f364ebc3247</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,645 +2761,2115 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a2f78c4c8ef75c2</t>
+          <t>https://www.indeed.com/viewjob?jk=ef9c01896959f630</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Engineer - Long Beach, CA</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e11fa47875d4b9f</t>
+          <t>https://www.indeed.com/viewjob?jk=271061dada6a961f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Computer Data Engineering Intern/Co-Op</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>StandardAero</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Spark, SQL Server, PostgreSQL, MySQL, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a982d1d82cbd60b</t>
+          <t>https://www.indeed.com/viewjob?jk=1faf6e04fa2bbdcf</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426cdfa391f3efd4</t>
+          <t>https://www.indeed.com/viewjob?jk=f9794568eb039870</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Ontology Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=178a5e6f1886f45d</t>
+          <t>https://www.indeed.com/viewjob?jk=1560887d7cb316fd</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Python Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6d21f70ad7aca36</t>
+          <t>https://www.indeed.com/viewjob?jk=bdd4ac5f09111b4e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr Software Developer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ELEVI Associates, LLC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, Scala, PostgreSQL, DynamoDB, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bef5e0cbd24f1e8d</t>
+          <t>https://www.indeed.com/viewjob?jk=dee274917e4b9029</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer (Business Intelligence) - Hybrid</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Scala, Snowflake, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b876b640329d1da8</t>
+          <t>https://www.indeed.com/viewjob?jk=2c1f0804f082a435</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>inversion</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fdf01ee46ca5c04</t>
+          <t>https://www.indeed.com/viewjob?jk=2bcfef10dd24abe4</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c66d1722dc1904af</t>
+          <t>https://www.indeed.com/viewjob?jk=71d3b83605c8a2df</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Knowtion Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>S3, Azure, Data Factory, Scala, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe12ac26edf139f6</t>
+          <t>https://www.indeed.com/viewjob?jk=940dcb7683294d7b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. Software Architect</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Applied Information Sciences</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, AKS</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef11c58ff0ce6339</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb60bebb7779e64</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>AiPrise</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Terraform, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=321ab7e09526522f</t>
+          <t>https://www.indeed.com/viewjob?jk=c37d2114cee6dba4</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Application Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, ECS, Databricks, Snowflake, PostgreSQL, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b1d7e70102157f1</t>
+          <t>https://www.indeed.com/viewjob?jk=c39c8b726cdb22aa</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. Associate Software Engineer (Healthcare Data Integration)</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5cc7c095dc341df</t>
+          <t>https://www.indeed.com/viewjob?jk=bd9a756aa23e011c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Full Stack AI Developer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Invovia</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, NoSQL, pytest</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e01424994cfb3518</t>
+          <t>https://www.indeed.com/viewjob?jk=22d070dab1e1cb93</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>[Remote] Senior FullStack Platform Software Engineer- Clinical Digital Assistant</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1a152297c2ff6df</t>
+          <t>https://www.indeed.com/viewjob?jk=4045cf1c680be7b6</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Business Applications Developer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>LeMaitre Vascular</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Azure, Data Lake Storage, Spark, PySpark, Scala, SQL Server, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a14f1f112ff2b5af</t>
+          <t>https://www.indeed.com/viewjob?jk=d5f4daad7fda9ff7</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>Software Engineer - Search and Personalization</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>MO, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0671107537ae859</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Software Engineer - Search and Personalization</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ME, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a057a8d1dc27a54f</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Software Engineer - Search and Personalization</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>UT, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ec8eebe082d41ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Software Engineer - Search and Personalization</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3912346602551520</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Software Engineer - Search and Personalization</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>AL, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0c6b2ae9b514e3c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Software Engineer - Search and Personalization</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>CO, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cdeb6923f62c2160</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Software Engineer - Search and Personalization</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>RI, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e8bc2ea076a0ded7</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Software Engineer - Search and Personalization</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>MT, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee0fd3306ac2ce34</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Solutions Architect - Financial Services (Insurance)</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2e4b10d02c9169d</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Sr. Solutions Architect - Financial Services (Wealth and Asset Management)</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f8502da83b9f3f55</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Snowflake Architect</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Aqua Finance</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>RDS, Cloud Storage, Scala, Snowflake, Time Travel, clustering keys, Data Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc4122f34f0b0a80</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Brown &amp; Brown Insurance</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f55a36c486ae8573</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Senior Guidewire Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Office Ally</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Walnut Creek, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e37631ce8845786</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior Guidewire Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Office Ally</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Concord, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0e4bf24557f7446</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Senior Guidewire Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Office Ally</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Clayton, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=943f1767bc3da17e</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Senior Guidewire Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Office Ally</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Antioch, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55a3ba405f74d032</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Senior Guidewire Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Office Ally</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Martinez, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53e9315332f2ea0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Senior Guidewire Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Office Ally</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Pleasant Hill, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ae88819d628f2aed</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Senior Guidewire Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Office Ally</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48ff3521016f8dd5</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93bbd1487e7d0fd7</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Data Analyst (Data Solutions)</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>The Coca-Cola Company</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa2ec42f2e29989e</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Sonny's Enterprises, Inc</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f7c892f9988b1e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Threat Detection Engineer – Security Operations</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>ID.me</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c29685a938223251</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Threat Detection Engineer – Security Operations</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>ID.me</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92a7ce3bbe941f36</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Threat Detection Engineer – Security Operations</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>ID.me</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a2f78c4c8ef75c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Sr. Business Intelligence Engineer - Long Beach, CA</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Hydrafacial</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Long Beach, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e11fa47875d4b9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Computer Data Engineering Intern/Co-Op</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>StandardAero</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Hadoop, Spark, SQL Server, PostgreSQL, MySQL, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a982d1d82cbd60b</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Analytics Developer, Enterprise Analytics (Data Shared Services)</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>NewYork-Presbyterian Hospital</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Manhattan, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, Power BI, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a889968da2ddc13e</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst - Corporate Financial</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>oura</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Unity Catalog, Scala, Snowflake, Dimensional Modeling, dbt, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0d0e3250352dd44</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Python Engineer</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Globant</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6d21f70ad7aca36</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Ontology Engineer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Stellantis</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Auburn Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=178a5e6f1886f45d</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Sr Software Developer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>ELEVI Associates, LLC</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Fort Meade, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, API Gateway, Scala, PostgreSQL, DynamoDB, CI/CD, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bef5e0cbd24f1e8d</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Data Engineer (Business Intelligence) - Hybrid</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Blue Cross Blue Shield of Arizona</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Scala, Snowflake, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b876b640329d1da8</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>inversion</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5fdf01ee46ca5c04</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Axon</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Blob Storage, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Terraform</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c66d1722dc1904af</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Knowtion Health</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>S3, Azure, Data Factory, Scala, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe12ac26edf139f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Sr. Software Architect</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Applied Information Sciences</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, AKS</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef11c58ff0ce6339</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>AiPrise</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Terraform, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=321ab7e09526522f</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Sr. Associate Software Engineer (Healthcare Data Integration)</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>McKesson</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c5cc7c095dc341df</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Full Stack AI Developer</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Invovia</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, NoSQL, pytest</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e01424994cfb3518</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>[Remote] Senior FullStack Platform Software Engineer- Clinical Digital Assistant</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1a152297c2ff6df</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Senior Application Engineer</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Lake Buena Vista, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Redshift, ECS, Databricks, Snowflake, PostgreSQL, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b1d7e70102157f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
           <t>Storage Engineer</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B127" t="inlineStr">
         <is>
           <t>JetBlue</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C127" t="inlineStr">
         <is>
           <t>Long Island City, NY, US USA</t>
         </is>
       </c>
-      <c r="D85" t="n">
+      <c r="D127" t="n">
         <v>10.4</v>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E127" t="inlineStr">
         <is>
           <t>AWS, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Oracle, SQL Server, Kubernetes</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5431a909ca95c9b1</t>
         </is>

--- a/results/job_matches_2026-06-26.xlsx
+++ b/results/job_matches_2026-06-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,60 +538,60 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer, Data - FreeWheel</t>
+          <t>Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Maverick Payments</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Hadoop, HDFS, Spark, Scala, Kafka</t>
+          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9de4453bf3c4212f</t>
+          <t>https://www.indeed.com/viewjob?jk=f9912f562ebafa77</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Warehouse Engineer</t>
+          <t>Engineer/Sr Engineer, IT Data</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Maverick Payments</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9912f562ebafa77</t>
+          <t>https://www.indeed.com/viewjob?jk=171509f615b5daa2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Data</t>
+          <t>Senior Software Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>ComplexCare Solutions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171509f615b5daa2</t>
+          <t>https://www.indeed.com/viewjob?jk=a32a20237152630a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Data Engineer (Contract)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ComplexCare Solutions</t>
+          <t>Atlas Group LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a32a20237152630a</t>
+          <t>https://www.indeed.com/viewjob?jk=96986685e9f66259</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Advisory Associate, AI - Summer 2026 (Houston)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Atlas Group LLC</t>
+          <t>BDO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Azure, Data Factory, Databricks</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96986685e9f66259</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5fd57bbd10ca27</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Advisory Associate, AI - Summer 2026 (Houston)</t>
+          <t>Senior Data Scientist – Manufacturing Intelligence, Machine Learning &amp; AI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BDO</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Wa-Ni Village, TN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Azure, Data Factory, Databricks</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f5fd57bbd10ca27</t>
+          <t>https://www.indeed.com/viewjob?jk=2ab95f94071e971b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Manufacturing Intelligence, Machine Learning &amp; AI</t>
+          <t>Artificial Intelligence/Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wa-Ni Village, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ab95f94071e971b</t>
+          <t>https://www.indeed.com/viewjob?jk=a074a785ce24052f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>U.S. Financial Technology</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a074a785ce24052f</t>
+          <t>https://www.indeed.com/viewjob?jk=a593e5a13bf91848</t>
         </is>
       </c>
     </row>
@@ -888,52 +888,52 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PLM Teamcenter Solution Architect - Siemens</t>
+          <t>Technology Architect - Product Development</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TAN45 TECH</t>
+          <t>Shearwater Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=747fddb8b55540ea</t>
+          <t>https://www.indeed.com/viewjob?jk=53d40e3111fd3799</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Technology Architect - Product Development</t>
+          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Shearwater Health</t>
+          <t>Mindful Support Services</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Mountlake Terrace, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53d40e3111fd3799</t>
+          <t>https://www.indeed.com/viewjob?jk=650467e40b62799c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mindful Support Services</t>
+          <t>Globant</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mountlake Terrace, WA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Hadoop, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=650467e40b62799c</t>
+          <t>https://www.indeed.com/viewjob?jk=0725cc4f521729f5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Solutions Engineer - Hybrid/Durham,NC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Hadoop, Spark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0725cc4f521729f5</t>
+          <t>https://www.indeed.com/viewjob?jk=f85d13cad9b24073</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer - Hybrid/Durham,NC</t>
+          <t>Senior Data Engineer, AI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85d13cad9b24073</t>
+          <t>https://www.indeed.com/viewjob?jk=e0ab478702c96db5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI</t>
+          <t>DevOps Engineer with Java</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0ab478702c96db5</t>
+          <t>https://www.indeed.com/viewjob?jk=91621af2058bcdaf</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91621af2058bcdaf</t>
+          <t>https://www.indeed.com/viewjob?jk=e4043bb7b561d2d9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DevOps Engineer with Java</t>
+          <t>GCP Technical Specialist</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4043bb7b561d2d9</t>
+          <t>https://www.indeed.com/viewjob?jk=a829451037364106</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GCP Technical Specialist</t>
+          <t>Platform Solutions – Dallas – Associate, Software Engineering – 4208762</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Spark, Scala, Kafka, Snowflake, Oracle, Cassandra, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a829451037364106</t>
+          <t>https://www.indeed.com/viewjob?jk=440eb7ec7c9d835a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Business Intelligence Sr Analyst</t>
+          <t>Senior Backend Software Engineer IV</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>Vida Health</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Snowflake</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e1d0952eadd1803</t>
+          <t>https://www.indeed.com/viewjob?jk=3a816a575de11cfe</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Platform Solutions – Dallas – Associate, Software Engineering – 4208762</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Mourant</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, Snowflake, Oracle, Cassandra, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,59 +1266,59 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=440eb7ec7c9d835a</t>
+          <t>https://www.indeed.com/viewjob?jk=bba01ebafe36cd2b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer IV</t>
+          <t>Senior Java Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vida Health</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, RDS, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a816a575de11cfe</t>
+          <t>https://www.indeed.com/viewjob?jk=ec4bd51618d0a580</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-Stack Java Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mourant</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, Kafka, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bba01ebafe36cd2b</t>
+          <t>https://www.indeed.com/viewjob?jk=651520622efc1265</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Java Engineer</t>
+          <t>IT Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>Nexzentek</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, RDS, Scala, Kafka, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec4bd51618d0a580</t>
+          <t>https://www.indeed.com/viewjob?jk=b58e4f761ccad015</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full-Stack Java Developer</t>
+          <t>Senior Software Engineer - 2373458</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, Kafka, PostgreSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=651520622efc1265</t>
+          <t>https://www.indeed.com/viewjob?jk=ff932a257a601c95</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IT Software Engineer</t>
+          <t>Senior Robotics Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nexzentek</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, Cassandra, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b58e4f761ccad015</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d4e995adafbb96</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - 2373458</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Coastal</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff932a257a601c95</t>
+          <t>https://www.indeed.com/viewjob?jk=a700c4126f5f39e0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Coastal</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a700c4126f5f39e0</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed62df8d733ccc6</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Cumming Group</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Murrieta, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed62df8d733ccc6</t>
+          <t>https://www.indeed.com/viewjob?jk=c2c1772ff77b54bf</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Cumming Group</t>
+          <t>Escalent</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Murrieta, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2c1772ff77b54bf</t>
+          <t>https://www.indeed.com/viewjob?jk=72ced5e68aed0c4e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Senior Integration Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Escalent</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,42 +1606,42 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Splunk, CI/CD, Maven, Git</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72ced5e68aed0c4e</t>
+          <t>https://www.indeed.com/viewjob?jk=7ce4996222dad233</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>Data Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Splunk, CI/CD, Maven, Git</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ce4996222dad233</t>
+          <t>https://www.indeed.com/viewjob?jk=6c63a2ab17c26b27</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer II - Global Servicing Technology</t>
+          <t>Data Engineer, Finance</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c63a2ab17c26b27</t>
+          <t>https://www.indeed.com/viewjob?jk=a49c234a0c6d1d83</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer, Finance</t>
+          <t>Sr Software Engineer I</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, ETL</t>
+          <t>AWS, RDS, HBase, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a49c234a0c6d1d83</t>
+          <t>https://www.indeed.com/viewjob?jk=b11810a6c43504b5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b11810a6c43504b5</t>
+          <t>https://www.indeed.com/viewjob?jk=58e6cb2128aca867</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>MNTN</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e6cb2128aca867</t>
+          <t>https://www.indeed.com/viewjob?jk=3610cfdfc0364b8e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MNTN</t>
+          <t>Crate and Barrel</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3610cfdfc0364b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=7e58f6e8fec3f48d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Crate and Barrel</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Git</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e58f6e8fec3f48d</t>
+          <t>https://www.indeed.com/viewjob?jk=cab0fb5e8b841018</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,17 +1886,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab0fb5e8b841018</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9a38e235659081</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9a38e235659081</t>
+          <t>https://www.indeed.com/viewjob?jk=cd0775a42f899524</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd0775a42f899524</t>
+          <t>https://www.indeed.com/viewjob?jk=b33138f7850dfefc</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b33138f7850dfefc</t>
+          <t>https://www.indeed.com/viewjob?jk=a342726a84e27f8e</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a342726a84e27f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=c186d8b7ac65fdf8</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c186d8b7ac65fdf8</t>
+          <t>https://www.indeed.com/viewjob?jk=95cc142f3e2617a6</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95cc142f3e2617a6</t>
+          <t>https://www.indeed.com/viewjob?jk=db16f20add9ea986</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db16f20add9ea986</t>
+          <t>https://www.indeed.com/viewjob?jk=1382d06b80fb6867</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1382d06b80fb6867</t>
+          <t>https://www.indeed.com/viewjob?jk=bcad5c4e643319ff</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcad5c4e643319ff</t>
+          <t>https://www.indeed.com/viewjob?jk=40e64526422d931b</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e64526422d931b</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d627fd3422104c</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d627fd3422104c</t>
+          <t>https://www.indeed.com/viewjob?jk=fab8211cf6bde1e0</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fab8211cf6bde1e0</t>
+          <t>https://www.indeed.com/viewjob?jk=05bab721c73d545f</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bab721c73d545f</t>
+          <t>https://www.indeed.com/viewjob?jk=85a706af297ba804</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85a706af297ba804</t>
+          <t>https://www.indeed.com/viewjob?jk=13401bc8d0f3279e</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13401bc8d0f3279e</t>
+          <t>https://www.indeed.com/viewjob?jk=31032458d140d1ae</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31032458d140d1ae</t>
+          <t>https://www.indeed.com/viewjob?jk=115cfe00112809d8</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=115cfe00112809d8</t>
+          <t>https://www.indeed.com/viewjob?jk=031a5b8865d1f458</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=031a5b8865d1f458</t>
+          <t>https://www.indeed.com/viewjob?jk=65c6bb88e77fa7e3</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65c6bb88e77fa7e3</t>
+          <t>https://www.indeed.com/viewjob?jk=0426526011ecf8ab</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0426526011ecf8ab</t>
+          <t>https://www.indeed.com/viewjob?jk=e2f4ae59bb2e76db</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2f4ae59bb2e76db</t>
+          <t>https://www.indeed.com/viewjob?jk=fc596e52195e0933</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc596e52195e0933</t>
+          <t>https://www.indeed.com/viewjob?jk=44f8b5180e01e140</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44f8b5180e01e140</t>
+          <t>https://www.indeed.com/viewjob?jk=af0b8f364ebc3247</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0b8f364ebc3247</t>
+          <t>https://www.indeed.com/viewjob?jk=ef9c01896959f630</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef9c01896959f630</t>
+          <t>https://www.indeed.com/viewjob?jk=271061dada6a961f</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271061dada6a961f</t>
+          <t>https://www.indeed.com/viewjob?jk=1faf6e04fa2bbdcf</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1faf6e04fa2bbdcf</t>
+          <t>https://www.indeed.com/viewjob?jk=f9794568eb039870</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9794568eb039870</t>
+          <t>https://www.indeed.com/viewjob?jk=1560887d7cb316fd</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1560887d7cb316fd</t>
+          <t>https://www.indeed.com/viewjob?jk=bdd4ac5f09111b4e</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd4ac5f09111b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=dee274917e4b9029</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dee274917e4b9029</t>
+          <t>https://www.indeed.com/viewjob?jk=2c1f0804f082a435</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c1f0804f082a435</t>
+          <t>https://www.indeed.com/viewjob?jk=2bcfef10dd24abe4</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bcfef10dd24abe4</t>
+          <t>https://www.indeed.com/viewjob?jk=71d3b83605c8a2df</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d3b83605c8a2df</t>
+          <t>https://www.indeed.com/viewjob?jk=940dcb7683294d7b</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=940dcb7683294d7b</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb60bebb7779e64</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbb60bebb7779e64</t>
+          <t>https://www.indeed.com/viewjob?jk=c37d2114cee6dba4</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37d2114cee6dba4</t>
+          <t>https://www.indeed.com/viewjob?jk=c39c8b726cdb22aa</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39c8b726cdb22aa</t>
+          <t>https://www.indeed.com/viewjob?jk=bd9a756aa23e011c</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd9a756aa23e011c</t>
+          <t>https://www.indeed.com/viewjob?jk=22d070dab1e1cb93</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22d070dab1e1cb93</t>
+          <t>https://www.indeed.com/viewjob?jk=4045cf1c680be7b6</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4045cf1c680be7b6</t>
+          <t>https://www.indeed.com/viewjob?jk=d5f4daad7fda9ff7</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f4daad7fda9ff7</t>
+          <t>https://www.indeed.com/viewjob?jk=d0671107537ae859</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0671107537ae859</t>
+          <t>https://www.indeed.com/viewjob?jk=a057a8d1dc27a54f</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a057a8d1dc27a54f</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec8eebe082d41ed</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec8eebe082d41ed</t>
+          <t>https://www.indeed.com/viewjob?jk=3912346602551520</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3912346602551520</t>
+          <t>https://www.indeed.com/viewjob?jk=0c6b2ae9b514e3c3</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c6b2ae9b514e3c3</t>
+          <t>https://www.indeed.com/viewjob?jk=cdeb6923f62c2160</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdeb6923f62c2160</t>
+          <t>https://www.indeed.com/viewjob?jk=e8bc2ea076a0ded7</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8bc2ea076a0ded7</t>
+          <t>https://www.indeed.com/viewjob?jk=ee0fd3306ac2ce34</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Solutions Architect - Financial Services (Insurance)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,24 +3636,24 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee0fd3306ac2ce34</t>
+          <t>https://www.indeed.com/viewjob?jk=c2e4b10d02c9169d</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Solutions Architect - Financial Services (Insurance)</t>
+          <t>Sr. Solutions Architect - Financial Services (Wealth and Asset Management)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2e4b10d02c9169d</t>
+          <t>https://www.indeed.com/viewjob?jk=f8502da83b9f3f55</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Financial Services (Wealth and Asset Management)</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Aqua Finance</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>RDS, Cloud Storage, Scala, Snowflake, Time Travel, clustering keys, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,19 +3716,19 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8502da83b9f3f55</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4122f34f0b0a80</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Aqua Finance</t>
+          <t>Brown &amp; Brown Insurance</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Cloud Storage, Scala, Snowflake, Time Travel, clustering keys, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4122f34f0b0a80</t>
+          <t>https://www.indeed.com/viewjob?jk=f55a36c486ae8573</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown Insurance</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f55a36c486ae8573</t>
+          <t>https://www.indeed.com/viewjob?jk=93bbd1487e7d0fd7</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Guidewire Integration Engineer</t>
+          <t>Data Analyst (Data Solutions)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e37631ce8845786</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2ec42f2e29989e</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Guidewire Integration Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Sonny's Enterprises, Inc</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0e4bf24557f7446</t>
+          <t>https://www.indeed.com/viewjob?jk=4f7c892f9988b1e9</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Guidewire Integration Engineer</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Clayton, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=943f1767bc3da17e</t>
+          <t>https://www.indeed.com/viewjob?jk=c29685a938223251</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Guidewire Integration Engineer</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Antioch, CA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55a3ba405f74d032</t>
+          <t>https://www.indeed.com/viewjob?jk=92a7ce3bbe941f36</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Guidewire Integration Engineer</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Martinez, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53e9315332f2ea0c</t>
+          <t>https://www.indeed.com/viewjob?jk=1a2f78c4c8ef75c2</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Guidewire Integration Engineer</t>
+          <t>Sr. Business Intelligence Engineer - Long Beach, CA</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Pleasant Hill, CA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae88819d628f2aed</t>
+          <t>https://www.indeed.com/viewjob?jk=3e11fa47875d4b9f</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Guidewire Integration Engineer</t>
+          <t>Computer Data Engineering Intern/Co-Op</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>StandardAero</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, ETL, Talend, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>RDS, Azure, Hadoop, Spark, SQL Server, PostgreSQL, MySQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48ff3521016f8dd5</t>
+          <t>https://www.indeed.com/viewjob?jk=4a982d1d82cbd60b</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Analytics Developer, Enterprise Analytics (Data Shared Services)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>NewYork-Presbyterian Hospital</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, Power BI, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93bbd1487e7d0fd7</t>
+          <t>https://www.indeed.com/viewjob?jk=a889968da2ddc13e</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data Analyst (Data Solutions)</t>
+          <t>Python Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Globant</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, Lambda, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,67 +4101,67 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2ec42f2e29989e</t>
+          <t>https://www.indeed.com/viewjob?jk=f6d21f70ad7aca36</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Ontology Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Sonny's Enterprises, Inc</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f7c892f9988b1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=178a5e6f1886f45d</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Data Engineer (Business Intelligence) - Hybrid</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Blue Cross Blue Shield of Arizona</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>RDS, Hadoop, Scala, Snowflake, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29685a938223251</t>
+          <t>https://www.indeed.com/viewjob?jk=b876b640329d1da8</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>inversion</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a7ce3bbe941f36</t>
+          <t>https://www.indeed.com/viewjob?jk=5fdf01ee46ca5c04</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, Azure, Blob Storage, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Terraform</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,67 +4241,67 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a2f78c4c8ef75c2</t>
+          <t>https://www.indeed.com/viewjob?jk=c66d1722dc1904af</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Engineer - Long Beach, CA</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>Knowtion Health</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
+          <t>S3, Azure, Data Factory, Scala, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e11fa47875d4b9f</t>
+          <t>https://www.indeed.com/viewjob?jk=fe12ac26edf139f6</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Computer Data Engineering Intern/Co-Op</t>
+          <t>Software Engineer III - Senior Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>StandardAero</t>
+          <t>AiPrise</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Spark, SQL Server, PostgreSQL, MySQL, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Terraform, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a982d1d82cbd60b</t>
+          <t>https://www.indeed.com/viewjob?jk=321ab7e09526522f</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Analytics Developer, Enterprise Analytics (Data Shared Services)</t>
+          <t>Sr. Associate Software Engineer (Healthcare Data Integration)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>NewYork-Presbyterian Hospital</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, Power BI, Azure DevOps, Git</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a889968da2ddc13e</t>
+          <t>https://www.indeed.com/viewjob?jk=c5cc7c095dc341df</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Data Analyst - Corporate Financial</t>
+          <t>Full Stack AI Developer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>oura</t>
+          <t>Invovia</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Scala, Snowflake, Dimensional Modeling, dbt, Power BI, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, NoSQL, pytest</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,67 +4381,67 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0d0e3250352dd44</t>
+          <t>https://www.indeed.com/viewjob?jk=e01424994cfb3518</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Python Engineer</t>
+          <t>[Remote] Senior FullStack Platform Software Engineer- Clinical Digital Assistant</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6d21f70ad7aca36</t>
+          <t>https://www.indeed.com/viewjob?jk=d1a152297c2ff6df</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Ontology Engineer</t>
+          <t>Senior Application Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Lambda, Redshift, ECS, Databricks, Snowflake, PostgreSQL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,427 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=178a5e6f1886f45d</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Sr Software Developer</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>ELEVI Associates, LLC</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Fort Meade, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, Scala, PostgreSQL, DynamoDB, CI/CD, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bef5e0cbd24f1e8d</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Data Engineer (Business Intelligence) - Hybrid</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Blue Cross Blue Shield of Arizona</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Scala, Snowflake, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b876b640329d1da8</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>inversion</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5fdf01ee46ca5c04</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Axon</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Blob Storage, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Terraform</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c66d1722dc1904af</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Knowtion Health</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>S3, Azure, Data Factory, Scala, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe12ac26edf139f6</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Sr. Software Architect</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Applied Information Sciences</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, AKS</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef11c58ff0ce6339</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>AiPrise</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Terraform, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=321ab7e09526522f</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Sr. Associate Software Engineer (Healthcare Data Integration)</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>McKesson</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c5cc7c095dc341df</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Full Stack AI Developer</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Invovia</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, NoSQL, pytest</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e01424994cfb3518</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>[Remote] Senior FullStack Platform Software Engineer- Clinical Digital Assistant</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d1a152297c2ff6df</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Senior Application Engineer</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>The Walt Disney Company</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Lake Buena Vista, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Redshift, ECS, Databricks, Snowflake, PostgreSQL, CI/CD, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=9b1d7e70102157f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Storage Engineer</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>JetBlue</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Long Island City, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Oracle, SQL Server, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5431a909ca95c9b1</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-26.xlsx
+++ b/results/job_matches_2026-06-26.xlsx
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Advisory Associate, AI - Summer 2026 (Houston)</t>
+          <t>Senior Data Scientist – Manufacturing Intelligence, Machine Learning &amp; AI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BDO</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Wa-Ni Village, TN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Azure, Data Factory, Databricks</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f5fd57bbd10ca27</t>
+          <t>https://www.indeed.com/viewjob?jk=2ab95f94071e971b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Manufacturing Intelligence, Machine Learning &amp; AI</t>
+          <t>Advisory Associate, AI - Summer 2026 (Houston)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>BDO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wa-Ni Village, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Azure, Data Factory, Databricks</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ab95f94071e971b</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5fd57bbd10ca27</t>
         </is>
       </c>
     </row>
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,17 +1851,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab0fb5e8b841018</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9a38e235659081</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9a38e235659081</t>
+          <t>https://www.indeed.com/viewjob?jk=cd0775a42f899524</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd0775a42f899524</t>
+          <t>https://www.indeed.com/viewjob?jk=b33138f7850dfefc</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b33138f7850dfefc</t>
+          <t>https://www.indeed.com/viewjob?jk=a342726a84e27f8e</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a342726a84e27f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=c186d8b7ac65fdf8</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c186d8b7ac65fdf8</t>
+          <t>https://www.indeed.com/viewjob?jk=95cc142f3e2617a6</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95cc142f3e2617a6</t>
+          <t>https://www.indeed.com/viewjob?jk=db16f20add9ea986</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db16f20add9ea986</t>
+          <t>https://www.indeed.com/viewjob?jk=1382d06b80fb6867</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1382d06b80fb6867</t>
+          <t>https://www.indeed.com/viewjob?jk=bcad5c4e643319ff</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcad5c4e643319ff</t>
+          <t>https://www.indeed.com/viewjob?jk=40e64526422d931b</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e64526422d931b</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d627fd3422104c</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d627fd3422104c</t>
+          <t>https://www.indeed.com/viewjob?jk=fab8211cf6bde1e0</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fab8211cf6bde1e0</t>
+          <t>https://www.indeed.com/viewjob?jk=05bab721c73d545f</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bab721c73d545f</t>
+          <t>https://www.indeed.com/viewjob?jk=85a706af297ba804</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85a706af297ba804</t>
+          <t>https://www.indeed.com/viewjob?jk=13401bc8d0f3279e</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13401bc8d0f3279e</t>
+          <t>https://www.indeed.com/viewjob?jk=31032458d140d1ae</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31032458d140d1ae</t>
+          <t>https://www.indeed.com/viewjob?jk=115cfe00112809d8</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=115cfe00112809d8</t>
+          <t>https://www.indeed.com/viewjob?jk=031a5b8865d1f458</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=031a5b8865d1f458</t>
+          <t>https://www.indeed.com/viewjob?jk=65c6bb88e77fa7e3</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65c6bb88e77fa7e3</t>
+          <t>https://www.indeed.com/viewjob?jk=0426526011ecf8ab</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0426526011ecf8ab</t>
+          <t>https://www.indeed.com/viewjob?jk=e2f4ae59bb2e76db</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2f4ae59bb2e76db</t>
+          <t>https://www.indeed.com/viewjob?jk=fc596e52195e0933</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc596e52195e0933</t>
+          <t>https://www.indeed.com/viewjob?jk=44f8b5180e01e140</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44f8b5180e01e140</t>
+          <t>https://www.indeed.com/viewjob?jk=af0b8f364ebc3247</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0b8f364ebc3247</t>
+          <t>https://www.indeed.com/viewjob?jk=ef9c01896959f630</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef9c01896959f630</t>
+          <t>https://www.indeed.com/viewjob?jk=271061dada6a961f</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271061dada6a961f</t>
+          <t>https://www.indeed.com/viewjob?jk=1faf6e04fa2bbdcf</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1faf6e04fa2bbdcf</t>
+          <t>https://www.indeed.com/viewjob?jk=f9794568eb039870</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9794568eb039870</t>
+          <t>https://www.indeed.com/viewjob?jk=1560887d7cb316fd</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1560887d7cb316fd</t>
+          <t>https://www.indeed.com/viewjob?jk=bdd4ac5f09111b4e</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd4ac5f09111b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=dee274917e4b9029</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dee274917e4b9029</t>
+          <t>https://www.indeed.com/viewjob?jk=2c1f0804f082a435</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c1f0804f082a435</t>
+          <t>https://www.indeed.com/viewjob?jk=2bcfef10dd24abe4</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bcfef10dd24abe4</t>
+          <t>https://www.indeed.com/viewjob?jk=71d3b83605c8a2df</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d3b83605c8a2df</t>
+          <t>https://www.indeed.com/viewjob?jk=940dcb7683294d7b</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=940dcb7683294d7b</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb60bebb7779e64</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbb60bebb7779e64</t>
+          <t>https://www.indeed.com/viewjob?jk=c37d2114cee6dba4</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37d2114cee6dba4</t>
+          <t>https://www.indeed.com/viewjob?jk=c39c8b726cdb22aa</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39c8b726cdb22aa</t>
+          <t>https://www.indeed.com/viewjob?jk=bd9a756aa23e011c</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd9a756aa23e011c</t>
+          <t>https://www.indeed.com/viewjob?jk=22d070dab1e1cb93</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22d070dab1e1cb93</t>
+          <t>https://www.indeed.com/viewjob?jk=4045cf1c680be7b6</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4045cf1c680be7b6</t>
+          <t>https://www.indeed.com/viewjob?jk=d5f4daad7fda9ff7</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f4daad7fda9ff7</t>
+          <t>https://www.indeed.com/viewjob?jk=d0671107537ae859</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0671107537ae859</t>
+          <t>https://www.indeed.com/viewjob?jk=a057a8d1dc27a54f</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a057a8d1dc27a54f</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec8eebe082d41ed</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec8eebe082d41ed</t>
+          <t>https://www.indeed.com/viewjob?jk=3912346602551520</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3912346602551520</t>
+          <t>https://www.indeed.com/viewjob?jk=0c6b2ae9b514e3c3</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c6b2ae9b514e3c3</t>
+          <t>https://www.indeed.com/viewjob?jk=cdeb6923f62c2160</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdeb6923f62c2160</t>
+          <t>https://www.indeed.com/viewjob?jk=e8bc2ea076a0ded7</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8bc2ea076a0ded7</t>
+          <t>https://www.indeed.com/viewjob?jk=ee0fd3306ac2ce34</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Solutions Architect - Financial Services (Insurance)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,24 +3601,24 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee0fd3306ac2ce34</t>
+          <t>https://www.indeed.com/viewjob?jk=c2e4b10d02c9169d</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Solutions Architect - Financial Services (Insurance)</t>
+          <t>Sr. Solutions Architect - Financial Services (Wealth and Asset Management)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2e4b10d02c9169d</t>
+          <t>https://www.indeed.com/viewjob?jk=f8502da83b9f3f55</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Financial Services (Wealth and Asset Management)</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Aqua Finance</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>RDS, Cloud Storage, Scala, Snowflake, Time Travel, clustering keys, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,19 +3681,19 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8502da83b9f3f55</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4122f34f0b0a80</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Aqua Finance</t>
+          <t>Brown &amp; Brown Insurance</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Cloud Storage, Scala, Snowflake, Time Travel, clustering keys, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4122f34f0b0a80</t>
+          <t>https://www.indeed.com/viewjob?jk=f55a36c486ae8573</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown Insurance</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f55a36c486ae8573</t>
+          <t>https://www.indeed.com/viewjob?jk=93bbd1487e7d0fd7</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93bbd1487e7d0fd7</t>
+          <t>https://www.indeed.com/viewjob?jk=c29685a938223251</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Analyst (Data Solutions)</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2ec42f2e29989e</t>
+          <t>https://www.indeed.com/viewjob?jk=92a7ce3bbe941f36</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Sonny's Enterprises, Inc</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f7c892f9988b1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=1a2f78c4c8ef75c2</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Data Analyst (Data Solutions)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29685a938223251</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2ec42f2e29989e</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Sonny's Enterprises, Inc</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,42 +3916,42 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a7ce3bbe941f36</t>
+          <t>https://www.indeed.com/viewjob?jk=4f7c892f9988b1e9</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Sr. Business Intelligence Engineer - Long Beach, CA</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a2f78c4c8ef75c2</t>
+          <t>https://www.indeed.com/viewjob?jk=3e11fa47875d4b9f</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Engineer - Long Beach, CA</t>
+          <t>Computer Data Engineering Intern/Co-Op</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>StandardAero</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
+          <t>RDS, Azure, Hadoop, Spark, SQL Server, PostgreSQL, MySQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e11fa47875d4b9f</t>
+          <t>https://www.indeed.com/viewjob?jk=4a982d1d82cbd60b</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Computer Data Engineering Intern/Co-Op</t>
+          <t>Systems Administrator - Junior</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>StandardAero</t>
+          <t>Alternative Information Systems</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,17 +4021,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Spark, SQL Server, PostgreSQL, MySQL, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a982d1d82cbd60b</t>
+          <t>https://www.indeed.com/viewjob?jk=87325485029af851</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-26.xlsx
+++ b/results/job_matches_2026-06-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Manufacturing Intelligence, Machine Learning &amp; AI</t>
+          <t>Advisory Associate, AI - Summer 2026 (Houston)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>BDO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wa-Ni Village, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Azure, Data Factory, Databricks</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ab95f94071e971b</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5fd57bbd10ca27</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Advisory Associate, AI - Summer 2026 (Houston)</t>
+          <t>Senior Data Scientist – Manufacturing Intelligence, Machine Learning &amp; AI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BDO</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Wa-Ni Village, TN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Azure, Data Factory, Databricks</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f5fd57bbd10ca27</t>
+          <t>https://www.indeed.com/viewjob?jk=2ab95f94071e971b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>U.S. Financial Technology</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a074a785ce24052f</t>
+          <t>https://www.indeed.com/viewjob?jk=a593e5a13bf91848</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>U.S. Financial Technology</t>
+          <t>Dematic</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,94 +811,94 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a593e5a13bf91848</t>
+          <t>https://www.indeed.com/viewjob?jk=f9bde3d8a51e4f79</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Spanner Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dematic</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Kafka, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9bde3d8a51e4f79</t>
+          <t>https://www.indeed.com/viewjob?jk=76401a227b65d3e8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GCP Spanner Data Engineer</t>
+          <t>Technology Architect - Product Development</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Shearwater Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Kafka, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76401a227b65d3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=53d40e3111fd3799</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Technology Architect - Product Development</t>
+          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Shearwater Health</t>
+          <t>Mindful Support Services</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Mountlake Terrace, WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,69 +906,69 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53d40e3111fd3799</t>
+          <t>https://www.indeed.com/viewjob?jk=650467e40b62799c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
+          <t>Data Engineer Senior - Big Data Platform Team</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mindful Support Services</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mountlake Terrace, WA, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>S3, RDS, Azure, Spark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=650467e40b62799c</t>
+          <t>https://www.indeed.com/viewjob?jk=0bd359ddd135794e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Solutions Engineer - Hybrid/Durham,NC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Hadoop, Spark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0725cc4f521729f5</t>
+          <t>https://www.indeed.com/viewjob?jk=f85d13cad9b24073</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer - Hybrid/Durham,NC</t>
+          <t>Senior Data Engineer, AI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85d13cad9b24073</t>
+          <t>https://www.indeed.com/viewjob?jk=e0ab478702c96db5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI</t>
+          <t>GCP Technical Specialist</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0ab478702c96db5</t>
+          <t>https://www.indeed.com/viewjob?jk=a829451037364106</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DevOps Engineer with Java</t>
+          <t>Platform Solutions – Dallas – Associate, Software Engineering – 4208762</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Spark, Scala, Kafka, Snowflake, Oracle, Cassandra, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91621af2058bcdaf</t>
+          <t>https://www.indeed.com/viewjob?jk=440eb7ec7c9d835a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DevOps Engineer with Java</t>
+          <t>Senior Backend Software Engineer IV</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Vida Health</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4043bb7b561d2d9</t>
+          <t>https://www.indeed.com/viewjob?jk=3a816a575de11cfe</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GCP Technical Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Mourant</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a829451037364106</t>
+          <t>https://www.indeed.com/viewjob?jk=bba01ebafe36cd2b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Platform Solutions – Dallas – Associate, Software Engineering – 4208762</t>
+          <t>Senior Java Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, Snowflake, Oracle, Cassandra, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, RDS, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=440eb7ec7c9d835a</t>
+          <t>https://www.indeed.com/viewjob?jk=ec4bd51618d0a580</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer IV</t>
+          <t>Senior Software Engineer - 2373458</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vida Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a816a575de11cfe</t>
+          <t>https://www.indeed.com/viewjob?jk=ff932a257a601c95</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-Stack Java Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mourant</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, Kafka, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bba01ebafe36cd2b</t>
+          <t>https://www.indeed.com/viewjob?jk=651520622efc1265</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Java Engineer</t>
+          <t>IT Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>Nexzentek</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,64 +1291,64 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, RDS, Scala, Kafka, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec4bd51618d0a580</t>
+          <t>https://www.indeed.com/viewjob?jk=b58e4f761ccad015</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Full-Stack Java Developer</t>
+          <t>Senior Robotics Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, Kafka, PostgreSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, Cassandra, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=651520622efc1265</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d4e995adafbb96</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IT Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nexzentek</t>
+          <t>Coastal</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1357,11 +1357,11 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,59 +1371,59 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b58e4f761ccad015</t>
+          <t>https://www.indeed.com/viewjob?jk=a700c4126f5f39e0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - 2373458</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>New York City Department of Sanitation</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>RDS, Databricks, Spark, PySpark, Informatica PowerCenter, Oracle, Data Modeling, ETL, ELT, Pentaho</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff932a257a601c95</t>
+          <t>https://www.indeed.com/viewjob?jk=f58c8be3a69d599b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Robotics Data Engineer/Data Scientist</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Cumming Group</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Murrieta, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,29 +1431,29 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, Cassandra, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d4e995adafbb96</t>
+          <t>https://www.indeed.com/viewjob?jk=c2c1772ff77b54bf</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Coastal</t>
+          <t>Escalent</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a700c4126f5f39e0</t>
+          <t>https://www.indeed.com/viewjob?jk=72ced5e68aed0c4e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Integration Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Splunk, CI/CD, Maven, Git</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed62df8d733ccc6</t>
+          <t>https://www.indeed.com/viewjob?jk=7ce4996222dad233</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Data Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cumming Group</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Murrieta, CA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,67 +1546,67 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2c1772ff77b54bf</t>
+          <t>https://www.indeed.com/viewjob?jk=6c63a2ab17c26b27</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Data Engineer, Finance</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Escalent</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72ced5e68aed0c4e</t>
+          <t>https://www.indeed.com/viewjob?jk=a49c234a0c6d1d83</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>Sr Software Engineer I</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Splunk, CI/CD, Maven, Git</t>
+          <t>AWS, RDS, HBase, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ce4996222dad233</t>
+          <t>https://www.indeed.com/viewjob?jk=b11810a6c43504b5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer II - Global Servicing Technology</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>MNTN</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c63a2ab17c26b27</t>
+          <t>https://www.indeed.com/viewjob?jk=3610cfdfc0364b8e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer, Finance</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>Crate and Barrel</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, ETL</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a49c234a0c6d1d83</t>
+          <t>https://www.indeed.com/viewjob?jk=7e58f6e8fec3f48d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b11810a6c43504b5</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9a38e235659081</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e6cb2128aca867</t>
+          <t>https://www.indeed.com/viewjob?jk=cd0775a42f899524</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MNTN</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3610cfdfc0364b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=b33138f7850dfefc</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Crate and Barrel</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e58f6e8fec3f48d</t>
+          <t>https://www.indeed.com/viewjob?jk=a342726a84e27f8e</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9a38e235659081</t>
+          <t>https://www.indeed.com/viewjob?jk=c186d8b7ac65fdf8</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd0775a42f899524</t>
+          <t>https://www.indeed.com/viewjob?jk=95cc142f3e2617a6</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b33138f7850dfefc</t>
+          <t>https://www.indeed.com/viewjob?jk=db16f20add9ea986</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a342726a84e27f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=1382d06b80fb6867</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c186d8b7ac65fdf8</t>
+          <t>https://www.indeed.com/viewjob?jk=bcad5c4e643319ff</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95cc142f3e2617a6</t>
+          <t>https://www.indeed.com/viewjob?jk=40e64526422d931b</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db16f20add9ea986</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d627fd3422104c</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1382d06b80fb6867</t>
+          <t>https://www.indeed.com/viewjob?jk=fab8211cf6bde1e0</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcad5c4e643319ff</t>
+          <t>https://www.indeed.com/viewjob?jk=05bab721c73d545f</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e64526422d931b</t>
+          <t>https://www.indeed.com/viewjob?jk=85a706af297ba804</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d627fd3422104c</t>
+          <t>https://www.indeed.com/viewjob?jk=13401bc8d0f3279e</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fab8211cf6bde1e0</t>
+          <t>https://www.indeed.com/viewjob?jk=31032458d140d1ae</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bab721c73d545f</t>
+          <t>https://www.indeed.com/viewjob?jk=115cfe00112809d8</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85a706af297ba804</t>
+          <t>https://www.indeed.com/viewjob?jk=031a5b8865d1f458</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13401bc8d0f3279e</t>
+          <t>https://www.indeed.com/viewjob?jk=65c6bb88e77fa7e3</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31032458d140d1ae</t>
+          <t>https://www.indeed.com/viewjob?jk=0426526011ecf8ab</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=115cfe00112809d8</t>
+          <t>https://www.indeed.com/viewjob?jk=e2f4ae59bb2e76db</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=031a5b8865d1f458</t>
+          <t>https://www.indeed.com/viewjob?jk=fc596e52195e0933</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65c6bb88e77fa7e3</t>
+          <t>https://www.indeed.com/viewjob?jk=44f8b5180e01e140</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0426526011ecf8ab</t>
+          <t>https://www.indeed.com/viewjob?jk=af0b8f364ebc3247</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2f4ae59bb2e76db</t>
+          <t>https://www.indeed.com/viewjob?jk=ef9c01896959f630</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc596e52195e0933</t>
+          <t>https://www.indeed.com/viewjob?jk=271061dada6a961f</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44f8b5180e01e140</t>
+          <t>https://www.indeed.com/viewjob?jk=1faf6e04fa2bbdcf</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0b8f364ebc3247</t>
+          <t>https://www.indeed.com/viewjob?jk=f9794568eb039870</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef9c01896959f630</t>
+          <t>https://www.indeed.com/viewjob?jk=1560887d7cb316fd</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271061dada6a961f</t>
+          <t>https://www.indeed.com/viewjob?jk=bdd4ac5f09111b4e</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1faf6e04fa2bbdcf</t>
+          <t>https://www.indeed.com/viewjob?jk=dee274917e4b9029</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9794568eb039870</t>
+          <t>https://www.indeed.com/viewjob?jk=2c1f0804f082a435</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1560887d7cb316fd</t>
+          <t>https://www.indeed.com/viewjob?jk=2bcfef10dd24abe4</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd4ac5f09111b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=71d3b83605c8a2df</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dee274917e4b9029</t>
+          <t>https://www.indeed.com/viewjob?jk=940dcb7683294d7b</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c1f0804f082a435</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb60bebb7779e64</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bcfef10dd24abe4</t>
+          <t>https://www.indeed.com/viewjob?jk=c37d2114cee6dba4</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d3b83605c8a2df</t>
+          <t>https://www.indeed.com/viewjob?jk=c39c8b726cdb22aa</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=940dcb7683294d7b</t>
+          <t>https://www.indeed.com/viewjob?jk=bd9a756aa23e011c</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbb60bebb7779e64</t>
+          <t>https://www.indeed.com/viewjob?jk=22d070dab1e1cb93</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37d2114cee6dba4</t>
+          <t>https://www.indeed.com/viewjob?jk=4045cf1c680be7b6</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39c8b726cdb22aa</t>
+          <t>https://www.indeed.com/viewjob?jk=d5f4daad7fda9ff7</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd9a756aa23e011c</t>
+          <t>https://www.indeed.com/viewjob?jk=d0671107537ae859</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22d070dab1e1cb93</t>
+          <t>https://www.indeed.com/viewjob?jk=a057a8d1dc27a54f</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4045cf1c680be7b6</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec8eebe082d41ed</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f4daad7fda9ff7</t>
+          <t>https://www.indeed.com/viewjob?jk=3912346602551520</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0671107537ae859</t>
+          <t>https://www.indeed.com/viewjob?jk=0c6b2ae9b514e3c3</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a057a8d1dc27a54f</t>
+          <t>https://www.indeed.com/viewjob?jk=cdeb6923f62c2160</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec8eebe082d41ed</t>
+          <t>https://www.indeed.com/viewjob?jk=e8bc2ea076a0ded7</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3912346602551520</t>
+          <t>https://www.indeed.com/viewjob?jk=ee0fd3306ac2ce34</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Solutions Architect - Financial Services (Insurance)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c6b2ae9b514e3c3</t>
+          <t>https://www.indeed.com/viewjob?jk=c2e4b10d02c9169d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Sr. Solutions Architect - Financial Services (Wealth and Asset Management)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdeb6923f62c2160</t>
+          <t>https://www.indeed.com/viewjob?jk=f8502da83b9f3f55</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Aqua Finance</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Cloud Storage, Scala, Snowflake, Time Travel, clustering keys, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8bc2ea076a0ded7</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4122f34f0b0a80</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Brown &amp; Brown Insurance</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee0fd3306ac2ce34</t>
+          <t>https://www.indeed.com/viewjob?jk=f55a36c486ae8573</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Solutions Architect - Financial Services (Insurance)</t>
+          <t>Data Analyst (Data Solutions)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2e4b10d02c9169d</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2ec42f2e29989e</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Financial Services (Wealth and Asset Management)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Sonny's Enterprises, Inc</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8502da83b9f3f55</t>
+          <t>https://www.indeed.com/viewjob?jk=4f7c892f9988b1e9</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Aqua Finance</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Cloud Storage, Scala, Snowflake, Time Travel, clustering keys, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4122f34f0b0a80</t>
+          <t>https://www.indeed.com/viewjob?jk=93bbd1487e7d0fd7</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown Insurance</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f55a36c486ae8573</t>
+          <t>https://www.indeed.com/viewjob?jk=c29685a938223251</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93bbd1487e7d0fd7</t>
+          <t>https://www.indeed.com/viewjob?jk=92a7ce3bbe941f36</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29685a938223251</t>
+          <t>https://www.indeed.com/viewjob?jk=1a2f78c4c8ef75c2</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Sr. Business Intelligence Engineer - Long Beach, CA</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a7ce3bbe941f36</t>
+          <t>https://www.indeed.com/viewjob?jk=3e11fa47875d4b9f</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Computer Data Engineering Intern/Co-Op</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>StandardAero</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>RDS, Azure, Hadoop, Spark, SQL Server, PostgreSQL, MySQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,94 +3856,94 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a2f78c4c8ef75c2</t>
+          <t>https://www.indeed.com/viewjob?jk=4a982d1d82cbd60b</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Analyst (Data Solutions)</t>
+          <t>Systems Administrator - Junior</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Alternative Information Systems</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2ec42f2e29989e</t>
+          <t>https://www.indeed.com/viewjob?jk=87325485029af851</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Sonny's Enterprises, Inc</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wausau, WI, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, RDS, Kafka, Snowflake, Oracle, ETL, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f7c892f9988b1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a4a5c971b6dae8</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Engineer - Long Beach, CA</t>
+          <t>Sr. Software Engineer, Enterprise Software</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e11fa47875d4b9f</t>
+          <t>https://www.indeed.com/viewjob?jk=424a613517dace69</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Computer Data Engineering Intern/Co-Op</t>
+          <t>Analytics Developer, Enterprise Analytics (Data Shared Services)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>StandardAero</t>
+          <t>NewYork-Presbyterian Hospital</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Spark, SQL Server, PostgreSQL, MySQL, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, Power BI, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a982d1d82cbd60b</t>
+          <t>https://www.indeed.com/viewjob?jk=a889968da2ddc13e</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Systems Administrator - Junior</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Alternative Information Systems</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, S3, Databricks, Kafka, Snowflake, PostgreSQL, Data Modeling, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87325485029af851</t>
+          <t>https://www.indeed.com/viewjob?jk=0309d0101fc2195f</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Analytics Developer, Enterprise Analytics (Data Shared Services)</t>
+          <t>Data Engineer (Business Intelligence) - Hybrid</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>NewYork-Presbyterian Hospital</t>
+          <t>Blue Cross Blue Shield of Arizona</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, Power BI, Azure DevOps, Git</t>
+          <t>RDS, Hadoop, Scala, Snowflake, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a889968da2ddc13e</t>
+          <t>https://www.indeed.com/viewjob?jk=b876b640329d1da8</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Python Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>inversion</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Terraform, Docker</t>
+          <t>AWS, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,59 +4101,59 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6d21f70ad7aca36</t>
+          <t>https://www.indeed.com/viewjob?jk=5fdf01ee46ca5c04</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Ontology Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Knowtion Health</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>S3, Azure, Data Factory, Scala, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=178a5e6f1886f45d</t>
+          <t>https://www.indeed.com/viewjob?jk=fe12ac26edf139f6</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Engineer (Business Intelligence) - Hybrid</t>
+          <t>Sr. Associate Software Engineer (Healthcare Data Integration)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Scala, Snowflake, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b876b640329d1da8</t>
+          <t>https://www.indeed.com/viewjob?jk=c5cc7c095dc341df</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Engineer III - Senior Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>inversion</t>
+          <t>AiPrise</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Terraform, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fdf01ee46ca5c04</t>
+          <t>https://www.indeed.com/viewjob?jk=321ab7e09526522f</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Full Stack AI Developer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Invovia</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, NoSQL, pytest</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,217 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c66d1722dc1904af</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Knowtion Health</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>S3, Azure, Data Factory, Scala, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe12ac26edf139f6</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Software Engineer III - Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>AiPrise</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Terraform, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=321ab7e09526522f</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Sr. Associate Software Engineer (Healthcare Data Integration)</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>McKesson</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c5cc7c095dc341df</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Full Stack AI Developer</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Invovia</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, NoSQL, pytest</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=e01424994cfb3518</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>[Remote] Senior FullStack Platform Software Engineer- Clinical Digital Assistant</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d1a152297c2ff6df</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Senior Application Engineer</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>The Walt Disney Company</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Lake Buena Vista, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Redshift, ECS, Databricks, Snowflake, PostgreSQL, CI/CD, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9b1d7e70102157f1</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-26.xlsx
+++ b/results/job_matches_2026-06-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IvoryCloud</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.8</v>
+        <v>21.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Azure, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c61bc90da42df2de</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b8b3a8aa7e371a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Palmetto Tech</t>
+          <t>IvoryCloud</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,19 +531,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d57ef47d055269a5</t>
+          <t>https://www.indeed.com/viewjob?jk=c61bc90da42df2de</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Warehouse Engineer</t>
+          <t>AWS Cloud</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Maverick Payments</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -556,42 +556,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9912f562ebafa77</t>
+          <t>https://www.indeed.com/viewjob?jk=9e552055c9acf50c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Data</t>
+          <t>Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Maverick Payments</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
+          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171509f615b5daa2</t>
+          <t>https://www.indeed.com/viewjob?jk=f9912f562ebafa77</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Data Engineer (Contract)</t>
+          <t>Engineer/Sr Engineer, IT Data</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ComplexCare Solutions</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a32a20237152630a</t>
+          <t>https://www.indeed.com/viewjob?jk=171509f615b5daa2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Software Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Atlas Group LLC</t>
+          <t>ComplexCare Solutions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96986685e9f66259</t>
+          <t>https://www.indeed.com/viewjob?jk=a32a20237152630a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Advisory Associate, AI - Summer 2026 (Houston)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BDO</t>
+          <t>Atlas Group LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Azure, Data Factory, Databricks</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f5fd57bbd10ca27</t>
+          <t>https://www.indeed.com/viewjob?jk=96986685e9f66259</t>
         </is>
       </c>
     </row>
@@ -783,130 +783,130 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dematic</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9bde3d8a51e4f79</t>
+          <t>https://www.indeed.com/viewjob?jk=c928b0a2d4a9c5fb</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GCP Spanner Data Engineer</t>
+          <t>Data Engineer Senior - Big Data Platform Team</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Kafka, NoSQL, ETL</t>
+          <t>S3, RDS, Azure, Spark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76401a227b65d3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=0bd359ddd135794e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Technology Architect - Product Development</t>
+          <t>Data Solutions Engineer - Hybrid/Durham,NC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Shearwater Health</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53d40e3111fd3799</t>
+          <t>https://www.indeed.com/viewjob?jk=f85d13cad9b24073</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
+          <t>Senior Data Engineer, AI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mindful Support Services</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mountlake Terrace, WA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=650467e40b62799c</t>
+          <t>https://www.indeed.com/viewjob?jk=e0ab478702c96db5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer Senior - Big Data Platform Team</t>
+          <t>GCP Technical Specialist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,112 +941,112 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Spark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bd359ddd135794e</t>
+          <t>https://www.indeed.com/viewjob?jk=a829451037364106</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer - Hybrid/Durham,NC</t>
+          <t>Software Engineer III (US)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85d13cad9b24073</t>
+          <t>https://www.indeed.com/viewjob?jk=d3f872ac99e6bd1a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI</t>
+          <t>Senior Software Engineer - Enterprise Data Services</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Wellmark Blue Cross and Blue Shield</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0ab478702c96db5</t>
+          <t>https://www.indeed.com/viewjob?jk=96ed3a70f59cd7a0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GCP Technical Specialist</t>
+          <t>Platform Solutions – Dallas – Associate, Software Engineering – 4208762</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Spark, Scala, Kafka, Snowflake, Oracle, Cassandra, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a829451037364106</t>
+          <t>https://www.indeed.com/viewjob?jk=440eb7ec7c9d835a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Platform Solutions – Dallas – Associate, Software Engineering – 4208762</t>
+          <t>Kafka Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, Snowflake, Oracle, Cassandra, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=440eb7ec7c9d835a</t>
+          <t>https://www.indeed.com/viewjob?jk=a7d027e8fdfa98b9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer IV</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vida Health</t>
+          <t>Mourant</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a816a575de11cfe</t>
+          <t>https://www.indeed.com/viewjob?jk=bba01ebafe36cd2b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-Stack Java Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mourant</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, Kafka, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bba01ebafe36cd2b</t>
+          <t>https://www.indeed.com/viewjob?jk=651520622efc1265</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Java Engineer</t>
+          <t>IT Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>Nexzentek</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,139 +1186,139 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, RDS, Scala, Kafka, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec4bd51618d0a580</t>
+          <t>https://www.indeed.com/viewjob?jk=b58e4f761ccad015</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - 2373458</t>
+          <t>Remote Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cloud Data Vision</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff932a257a601c95</t>
+          <t>https://www.indeed.com/viewjob?jk=b5be313cc3b61a58</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full-Stack Java Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>New York City Department of Sanitation</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, Kafka, PostgreSQL, Splunk, CI/CD</t>
+          <t>RDS, Databricks, Spark, PySpark, Informatica PowerCenter, Oracle, Data Modeling, ETL, ELT, Pentaho</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=651520622efc1265</t>
+          <t>https://www.indeed.com/viewjob?jk=f58c8be3a69d599b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IT Software Engineer</t>
+          <t>Senior Robotics Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nexzentek</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, Cassandra, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b58e4f761ccad015</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d4e995adafbb96</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Robotics Data Engineer/Data Scientist</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, Cassandra, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d4e995adafbb96</t>
+          <t>https://www.indeed.com/viewjob?jk=d54d860c68542f20</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>New York City Department of Sanitation</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Informatica PowerCenter, Oracle, Data Modeling, ETL, ELT, Pentaho</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f58c8be3a69d599b</t>
+          <t>https://www.indeed.com/viewjob?jk=c2c3ec644d917447</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Senior Integration Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cumming Group</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Murrieta, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Splunk, CI/CD, Maven, Git</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,77 +1441,77 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2c1772ff77b54bf</t>
+          <t>https://www.indeed.com/viewjob?jk=7ce4996222dad233</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Data Engineer, League Analytics &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Escalent</t>
+          <t>Major League Baseball</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72ced5e68aed0c4e</t>
+          <t>https://www.indeed.com/viewjob?jk=5e63e2ea97ff196b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>MNTN</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Splunk, CI/CD, Maven, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ce4996222dad233</t>
+          <t>https://www.indeed.com/viewjob?jk=3610cfdfc0364b8e</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Crate and Barrel</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b11810a6c43504b5</t>
+          <t>https://www.indeed.com/viewjob?jk=7e58f6e8fec3f48d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MNTN</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3610cfdfc0364b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9a38e235659081</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Crate and Barrel</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e58f6e8fec3f48d</t>
+          <t>https://www.indeed.com/viewjob?jk=cd0775a42f899524</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9a38e235659081</t>
+          <t>https://www.indeed.com/viewjob?jk=b33138f7850dfefc</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd0775a42f899524</t>
+          <t>https://www.indeed.com/viewjob?jk=a342726a84e27f8e</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b33138f7850dfefc</t>
+          <t>https://www.indeed.com/viewjob?jk=c186d8b7ac65fdf8</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a342726a84e27f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=95cc142f3e2617a6</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c186d8b7ac65fdf8</t>
+          <t>https://www.indeed.com/viewjob?jk=db16f20add9ea986</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95cc142f3e2617a6</t>
+          <t>https://www.indeed.com/viewjob?jk=1382d06b80fb6867</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db16f20add9ea986</t>
+          <t>https://www.indeed.com/viewjob?jk=bcad5c4e643319ff</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1382d06b80fb6867</t>
+          <t>https://www.indeed.com/viewjob?jk=40e64526422d931b</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcad5c4e643319ff</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d627fd3422104c</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e64526422d931b</t>
+          <t>https://www.indeed.com/viewjob?jk=fab8211cf6bde1e0</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d627fd3422104c</t>
+          <t>https://www.indeed.com/viewjob?jk=05bab721c73d545f</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fab8211cf6bde1e0</t>
+          <t>https://www.indeed.com/viewjob?jk=85a706af297ba804</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bab721c73d545f</t>
+          <t>https://www.indeed.com/viewjob?jk=13401bc8d0f3279e</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85a706af297ba804</t>
+          <t>https://www.indeed.com/viewjob?jk=31032458d140d1ae</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13401bc8d0f3279e</t>
+          <t>https://www.indeed.com/viewjob?jk=115cfe00112809d8</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31032458d140d1ae</t>
+          <t>https://www.indeed.com/viewjob?jk=031a5b8865d1f458</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=115cfe00112809d8</t>
+          <t>https://www.indeed.com/viewjob?jk=65c6bb88e77fa7e3</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=031a5b8865d1f458</t>
+          <t>https://www.indeed.com/viewjob?jk=0426526011ecf8ab</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65c6bb88e77fa7e3</t>
+          <t>https://www.indeed.com/viewjob?jk=e2f4ae59bb2e76db</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0426526011ecf8ab</t>
+          <t>https://www.indeed.com/viewjob?jk=fc596e52195e0933</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2f4ae59bb2e76db</t>
+          <t>https://www.indeed.com/viewjob?jk=44f8b5180e01e140</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc596e52195e0933</t>
+          <t>https://www.indeed.com/viewjob?jk=af0b8f364ebc3247</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44f8b5180e01e140</t>
+          <t>https://www.indeed.com/viewjob?jk=ef9c01896959f630</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0b8f364ebc3247</t>
+          <t>https://www.indeed.com/viewjob?jk=271061dada6a961f</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef9c01896959f630</t>
+          <t>https://www.indeed.com/viewjob?jk=1faf6e04fa2bbdcf</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271061dada6a961f</t>
+          <t>https://www.indeed.com/viewjob?jk=f9794568eb039870</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1faf6e04fa2bbdcf</t>
+          <t>https://www.indeed.com/viewjob?jk=1560887d7cb316fd</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9794568eb039870</t>
+          <t>https://www.indeed.com/viewjob?jk=bdd4ac5f09111b4e</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1560887d7cb316fd</t>
+          <t>https://www.indeed.com/viewjob?jk=dee274917e4b9029</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd4ac5f09111b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=2c1f0804f082a435</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dee274917e4b9029</t>
+          <t>https://www.indeed.com/viewjob?jk=2bcfef10dd24abe4</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c1f0804f082a435</t>
+          <t>https://www.indeed.com/viewjob?jk=71d3b83605c8a2df</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bcfef10dd24abe4</t>
+          <t>https://www.indeed.com/viewjob?jk=940dcb7683294d7b</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d3b83605c8a2df</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb60bebb7779e64</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=940dcb7683294d7b</t>
+          <t>https://www.indeed.com/viewjob?jk=c37d2114cee6dba4</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbb60bebb7779e64</t>
+          <t>https://www.indeed.com/viewjob?jk=c39c8b726cdb22aa</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37d2114cee6dba4</t>
+          <t>https://www.indeed.com/viewjob?jk=bd9a756aa23e011c</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39c8b726cdb22aa</t>
+          <t>https://www.indeed.com/viewjob?jk=22d070dab1e1cb93</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd9a756aa23e011c</t>
+          <t>https://www.indeed.com/viewjob?jk=4045cf1c680be7b6</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22d070dab1e1cb93</t>
+          <t>https://www.indeed.com/viewjob?jk=d5f4daad7fda9ff7</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4045cf1c680be7b6</t>
+          <t>https://www.indeed.com/viewjob?jk=d0671107537ae859</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f4daad7fda9ff7</t>
+          <t>https://www.indeed.com/viewjob?jk=a057a8d1dc27a54f</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0671107537ae859</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec8eebe082d41ed</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a057a8d1dc27a54f</t>
+          <t>https://www.indeed.com/viewjob?jk=3912346602551520</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec8eebe082d41ed</t>
+          <t>https://www.indeed.com/viewjob?jk=0c6b2ae9b514e3c3</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3912346602551520</t>
+          <t>https://www.indeed.com/viewjob?jk=cdeb6923f62c2160</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c6b2ae9b514e3c3</t>
+          <t>https://www.indeed.com/viewjob?jk=e8bc2ea076a0ded7</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdeb6923f62c2160</t>
+          <t>https://www.indeed.com/viewjob?jk=ee0fd3306ac2ce34</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,112 +3391,112 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8bc2ea076a0ded7</t>
+          <t>https://www.indeed.com/viewjob?jk=93bbd1487e7d0fd7</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Computer Data Engineering Intern/Co-Op</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>StandardAero</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, Hadoop, Spark, SQL Server, PostgreSQL, MySQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee0fd3306ac2ce34</t>
+          <t>https://www.indeed.com/viewjob?jk=4a982d1d82cbd60b</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Solutions Architect - Financial Services (Insurance)</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Plymouth, MI, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, MLOps, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2e4b10d02c9169d</t>
+          <t>https://www.indeed.com/viewjob?jk=f03c5058699b33f7</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Financial Services (Wealth and Asset Management)</t>
+          <t>Sr. Business Intelligence Engineer - Long Beach, CA</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,172 +3506,172 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8502da83b9f3f55</t>
+          <t>https://www.indeed.com/viewjob?jk=3e11fa47875d4b9f</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Systems Administrator - Junior</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Aqua Finance</t>
+          <t>Alternative Information Systems</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Cloud Storage, Scala, Snowflake, Time Travel, clustering keys, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4122f34f0b0a80</t>
+          <t>https://www.indeed.com/viewjob?jk=87325485029af851</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown Insurance</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f55a36c486ae8573</t>
+          <t>https://www.indeed.com/viewjob?jk=276c91b178e50bc3</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Analyst (Data Solutions)</t>
+          <t>Senior .net Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2ec42f2e29989e</t>
+          <t>https://www.indeed.com/viewjob?jk=2ec84c14bbe42215</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Sonny's Enterprises, Inc</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wausau, WI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, RDS, Kafka, Snowflake, Oracle, ETL, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f7c892f9988b1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a4a5c971b6dae8</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr. Software Engineer, Enterprise Software</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93bbd1487e7d0fd7</t>
+          <t>https://www.indeed.com/viewjob?jk=424a613517dace69</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Analytics Developer, Enterprise Analytics (Data Shared Services)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>NewYork-Presbyterian Hospital</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, Power BI, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,137 +3716,137 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29685a938223251</t>
+          <t>https://www.indeed.com/viewjob?jk=a889968da2ddc13e</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>OpenShift Platform Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a7ce3bbe941f36</t>
+          <t>https://www.indeed.com/viewjob?jk=8bfc9d48bb1fdefc</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Sustainability Data and AI Consultant</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Git, Python</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a2f78c4c8ef75c2</t>
+          <t>https://www.indeed.com/viewjob?jk=7976a31d4fb905fe</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Engineer - Long Beach, CA</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
+          <t>AWS, S3, Databricks, Kafka, Snowflake, PostgreSQL, Data Modeling, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e11fa47875d4b9f</t>
+          <t>https://www.indeed.com/viewjob?jk=0309d0101fc2195f</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Computer Data Engineering Intern/Co-Op</t>
+          <t>Data Engineer (Business Intelligence) - Hybrid</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>StandardAero</t>
+          <t>Blue Cross Blue Shield of Arizona</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Spark, SQL Server, PostgreSQL, MySQL, ETL, Power BI, Tableau</t>
+          <t>RDS, Hadoop, Scala, Snowflake, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,42 +3856,42 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a982d1d82cbd60b</t>
+          <t>https://www.indeed.com/viewjob?jk=b876b640329d1da8</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Systems Administrator - Junior</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Alternative Information Systems</t>
+          <t>inversion</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87325485029af851</t>
+          <t>https://www.indeed.com/viewjob?jk=5fdf01ee46ca5c04</t>
         </is>
       </c>
     </row>
@@ -3903,117 +3903,117 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Knowtion Health</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Wausau, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, Snowflake, Oracle, ETL, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>S3, Azure, Data Factory, Scala, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a4a5c971b6dae8</t>
+          <t>https://www.indeed.com/viewjob?jk=fe12ac26edf139f6</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Enterprise Software</t>
+          <t>Senior Software Engineer - Python/Agentic AI</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424a613517dace69</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2ba4e75ec79621</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Analytics Developer, Enterprise Analytics (Data Shared Services)</t>
+          <t>SecOps Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>NewYork-Presbyterian Hospital</t>
+          <t>Midwest Tape</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Holland, OH, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, Power BI, Azure DevOps, Git</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a889968da2ddc13e</t>
+          <t>https://www.indeed.com/viewjob?jk=965702c6436d9964</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineering Supervisor - Hybrid</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Sunrise Banks</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Kafka, Snowflake, PostgreSQL, Data Modeling, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, NoSQL, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0309d0101fc2195f</t>
+          <t>https://www.indeed.com/viewjob?jk=853197679fd8570c</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Engineer (Business Intelligence) - Hybrid</t>
+          <t>Sr. Associate Software Engineer (Healthcare Data Integration)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Scala, Snowflake, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b876b640329d1da8</t>
+          <t>https://www.indeed.com/viewjob?jk=c5cc7c095dc341df</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Engineer III - Senior Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>inversion</t>
+          <t>AiPrise</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Terraform, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,147 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fdf01ee46ca5c04</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Knowtion Health</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>S3, Azure, Data Factory, Scala, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe12ac26edf139f6</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Sr. Associate Software Engineer (Healthcare Data Integration)</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>McKesson</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c5cc7c095dc341df</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Software Engineer III - Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>AiPrise</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Terraform, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=321ab7e09526522f</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Full Stack AI Developer</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Invovia</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, NoSQL, pytest</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e01424994cfb3518</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-26.xlsx
+++ b/results/job_matches_2026-06-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IvoryCloud</t>
+          <t>Maverick Payments</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture</t>
+          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c61bc90da42df2de</t>
+          <t>https://www.indeed.com/viewjob?jk=f9912f562ebafa77</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS Cloud</t>
+          <t>Engineer/Sr Engineer, IT Data</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e552055c9acf50c</t>
+          <t>https://www.indeed.com/viewjob?jk=171509f615b5daa2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Warehouse Engineer</t>
+          <t>Senior Data Scientist – Manufacturing Intelligence, Machine Learning &amp; AI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Maverick Payments</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wa-Ni Village, TN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9912f562ebafa77</t>
+          <t>https://www.indeed.com/viewjob?jk=2ab95f94071e971b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Data</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171509f615b5daa2</t>
+          <t>https://www.indeed.com/viewjob?jk=efacd6764e780443</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Data Engineer (Contract)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ComplexCare Solutions</t>
+          <t>U.S. Financial Technology</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,129 +671,129 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a32a20237152630a</t>
+          <t>https://www.indeed.com/viewjob?jk=a593e5a13bf91848</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior IT Big Data Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Atlas Group LLC</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96986685e9f66259</t>
+          <t>https://www.indeed.com/viewjob?jk=ae26c12caca27959</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Manufacturing Intelligence, Machine Learning &amp; AI</t>
+          <t>Data Engineer Senior - Big Data Platform Team</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wa-Ni Village, TN, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>S3, RDS, Azure, Spark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ab95f94071e971b</t>
+          <t>https://www.indeed.com/viewjob?jk=0bd359ddd135794e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior IT Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>U.S. Financial Technology</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a593e5a13bf91848</t>
+          <t>https://www.indeed.com/viewjob?jk=efb360d7f7dedcd5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OCI Cloud Engineer</t>
+          <t>Data Solutions Engineer - Hybrid/Durham,NC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c928b0a2d4a9c5fb</t>
+          <t>https://www.indeed.com/viewjob?jk=f85d13cad9b24073</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer Senior - Big Data Platform Team</t>
+          <t>GCP Technical Specialist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,147 +836,147 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Spark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bd359ddd135794e</t>
+          <t>https://www.indeed.com/viewjob?jk=a829451037364106</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer - Hybrid/Durham,NC</t>
+          <t>Senior Software Engineer - Enterprise Data Services</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>Wellmark Blue Cross and Blue Shield</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85d13cad9b24073</t>
+          <t>https://www.indeed.com/viewjob?jk=96ed3a70f59cd7a0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI</t>
+          <t>Software Engineer III (US)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0ab478702c96db5</t>
+          <t>https://www.indeed.com/viewjob?jk=d3f872ac99e6bd1a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GCP Technical Specialist</t>
+          <t>Senior Consultant- Data/AI Due Diligence-MTS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a829451037364106</t>
+          <t>https://www.indeed.com/viewjob?jk=7b6bc1ec4cda3c8e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer III (US)</t>
+          <t>Professional Services Consultant</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,89 +986,89 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3f872ac99e6bd1a</t>
+          <t>https://www.indeed.com/viewjob?jk=9ba41961ffb1881c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Enterprise Data Services</t>
+          <t>Full-Stack Java Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, Kafka, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ed3a70f59cd7a0</t>
+          <t>https://www.indeed.com/viewjob?jk=651520622efc1265</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Platform Solutions – Dallas – Associate, Software Engineering – 4208762</t>
+          <t>Senior Robotics Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, Snowflake, Oracle, Cassandra, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, Cassandra, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=440eb7ec7c9d835a</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d4e995adafbb96</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kafka Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Coastal</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1077,143 +1077,143 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7d027e8fdfa98b9</t>
+          <t>https://www.indeed.com/viewjob?jk=a700c4126f5f39e0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mourant</t>
+          <t>Arc Technologies Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bba01ebafe36cd2b</t>
+          <t>https://www.indeed.com/viewjob?jk=8ccc63169a66ef59</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Full-Stack Java Developer</t>
+          <t>Remote Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Cloud Data Vision</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, Kafka, PostgreSQL, Splunk, CI/CD</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=651520622efc1265</t>
+          <t>https://www.indeed.com/viewjob?jk=b5be313cc3b61a58</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IT Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nexzentek</t>
+          <t>New York City Department of Sanitation</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>RDS, Databricks, Spark, PySpark, Informatica PowerCenter, Oracle, Data Modeling, ETL, ELT, Pentaho</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b58e4f761ccad015</t>
+          <t>https://www.indeed.com/viewjob?jk=f58c8be3a69d599b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Remote Kubernetes Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cloud Data Vision</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5be313cc3b61a58</t>
+          <t>https://www.indeed.com/viewjob?jk=d54d860c68542f20</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Developer Operations Engineer I</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>New York City Department of Sanitation</t>
+          <t>Transcor Data Services</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Informatica PowerCenter, Oracle, Data Modeling, ETL, ELT, Pentaho</t>
+          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f58c8be3a69d599b</t>
+          <t>https://www.indeed.com/viewjob?jk=b84e13a37c8822b9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Robotics Data Engineer/Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Univision Communications Inc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, Cassandra, Data Modeling</t>
+          <t>AWS, IAM, Google Cloud Platform, GCP, Hadoop, Spark, Scala, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,102 +1301,102 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d4e995adafbb96</t>
+          <t>https://www.indeed.com/viewjob?jk=b2f885fbfd483879</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d54d860c68542f20</t>
+          <t>https://www.indeed.com/viewjob?jk=6c63a2ab17c26b27</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer, League Analytics &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Coastal</t>
+          <t>Major League Baseball</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a700c4126f5f39e0</t>
+          <t>https://www.indeed.com/viewjob?jk=5e63e2ea97ff196b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>MNTN</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,59 +1406,59 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2c3ec644d917447</t>
+          <t>https://www.indeed.com/viewjob?jk=3610cfdfc0364b8e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Splunk, CI/CD, Maven, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ce4996222dad233</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9a38e235659081</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer, League Analytics &amp; Infrastructure</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Major League Baseball</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e63e2ea97ff196b</t>
+          <t>https://www.indeed.com/viewjob?jk=cd0775a42f899524</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MNTN</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3610cfdfc0364b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=b33138f7850dfefc</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer II - Global Servicing Technology</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c63a2ab17c26b27</t>
+          <t>https://www.indeed.com/viewjob?jk=a342726a84e27f8e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer, Finance</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a49c234a0c6d1d83</t>
+          <t>https://www.indeed.com/viewjob?jk=c186d8b7ac65fdf8</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Crate and Barrel</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e58f6e8fec3f48d</t>
+          <t>https://www.indeed.com/viewjob?jk=95cc142f3e2617a6</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9a38e235659081</t>
+          <t>https://www.indeed.com/viewjob?jk=db16f20add9ea986</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd0775a42f899524</t>
+          <t>https://www.indeed.com/viewjob?jk=1382d06b80fb6867</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b33138f7850dfefc</t>
+          <t>https://www.indeed.com/viewjob?jk=bcad5c4e643319ff</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a342726a84e27f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=40e64526422d931b</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c186d8b7ac65fdf8</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d627fd3422104c</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95cc142f3e2617a6</t>
+          <t>https://www.indeed.com/viewjob?jk=fab8211cf6bde1e0</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db16f20add9ea986</t>
+          <t>https://www.indeed.com/viewjob?jk=05bab721c73d545f</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1382d06b80fb6867</t>
+          <t>https://www.indeed.com/viewjob?jk=85a706af297ba804</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcad5c4e643319ff</t>
+          <t>https://www.indeed.com/viewjob?jk=13401bc8d0f3279e</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e64526422d931b</t>
+          <t>https://www.indeed.com/viewjob?jk=31032458d140d1ae</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d627fd3422104c</t>
+          <t>https://www.indeed.com/viewjob?jk=115cfe00112809d8</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fab8211cf6bde1e0</t>
+          <t>https://www.indeed.com/viewjob?jk=031a5b8865d1f458</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bab721c73d545f</t>
+          <t>https://www.indeed.com/viewjob?jk=65c6bb88e77fa7e3</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85a706af297ba804</t>
+          <t>https://www.indeed.com/viewjob?jk=0426526011ecf8ab</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13401bc8d0f3279e</t>
+          <t>https://www.indeed.com/viewjob?jk=e2f4ae59bb2e76db</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31032458d140d1ae</t>
+          <t>https://www.indeed.com/viewjob?jk=fc596e52195e0933</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=115cfe00112809d8</t>
+          <t>https://www.indeed.com/viewjob?jk=44f8b5180e01e140</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=031a5b8865d1f458</t>
+          <t>https://www.indeed.com/viewjob?jk=af0b8f364ebc3247</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65c6bb88e77fa7e3</t>
+          <t>https://www.indeed.com/viewjob?jk=ef9c01896959f630</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0426526011ecf8ab</t>
+          <t>https://www.indeed.com/viewjob?jk=271061dada6a961f</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2f4ae59bb2e76db</t>
+          <t>https://www.indeed.com/viewjob?jk=1faf6e04fa2bbdcf</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc596e52195e0933</t>
+          <t>https://www.indeed.com/viewjob?jk=f9794568eb039870</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44f8b5180e01e140</t>
+          <t>https://www.indeed.com/viewjob?jk=1560887d7cb316fd</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0b8f364ebc3247</t>
+          <t>https://www.indeed.com/viewjob?jk=bdd4ac5f09111b4e</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef9c01896959f630</t>
+          <t>https://www.indeed.com/viewjob?jk=dee274917e4b9029</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271061dada6a961f</t>
+          <t>https://www.indeed.com/viewjob?jk=2c1f0804f082a435</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1faf6e04fa2bbdcf</t>
+          <t>https://www.indeed.com/viewjob?jk=2bcfef10dd24abe4</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9794568eb039870</t>
+          <t>https://www.indeed.com/viewjob?jk=71d3b83605c8a2df</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1560887d7cb316fd</t>
+          <t>https://www.indeed.com/viewjob?jk=940dcb7683294d7b</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd4ac5f09111b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb60bebb7779e64</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dee274917e4b9029</t>
+          <t>https://www.indeed.com/viewjob?jk=c37d2114cee6dba4</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c1f0804f082a435</t>
+          <t>https://www.indeed.com/viewjob?jk=c39c8b726cdb22aa</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bcfef10dd24abe4</t>
+          <t>https://www.indeed.com/viewjob?jk=bd9a756aa23e011c</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d3b83605c8a2df</t>
+          <t>https://www.indeed.com/viewjob?jk=22d070dab1e1cb93</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=940dcb7683294d7b</t>
+          <t>https://www.indeed.com/viewjob?jk=4045cf1c680be7b6</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbb60bebb7779e64</t>
+          <t>https://www.indeed.com/viewjob?jk=d5f4daad7fda9ff7</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37d2114cee6dba4</t>
+          <t>https://www.indeed.com/viewjob?jk=d0671107537ae859</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39c8b726cdb22aa</t>
+          <t>https://www.indeed.com/viewjob?jk=a057a8d1dc27a54f</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd9a756aa23e011c</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec8eebe082d41ed</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22d070dab1e1cb93</t>
+          <t>https://www.indeed.com/viewjob?jk=3912346602551520</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4045cf1c680be7b6</t>
+          <t>https://www.indeed.com/viewjob?jk=0c6b2ae9b514e3c3</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f4daad7fda9ff7</t>
+          <t>https://www.indeed.com/viewjob?jk=cdeb6923f62c2160</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0671107537ae859</t>
+          <t>https://www.indeed.com/viewjob?jk=e8bc2ea076a0ded7</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a057a8d1dc27a54f</t>
+          <t>https://www.indeed.com/viewjob?jk=ee0fd3306ac2ce34</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Plymouth, MI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, MLOps, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,67 +3191,67 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec8eebe082d41ed</t>
+          <t>https://www.indeed.com/viewjob?jk=f03c5058699b33f7</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Computer Data Engineering Intern/Co-Op</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>StandardAero</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, Hadoop, Spark, SQL Server, PostgreSQL, MySQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3912346602551520</t>
+          <t>https://www.indeed.com/viewjob?jk=4a982d1d82cbd60b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c6b2ae9b514e3c3</t>
+          <t>https://www.indeed.com/viewjob?jk=276c91b178e50bc3</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Senior .net Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdeb6923f62c2160</t>
+          <t>https://www.indeed.com/viewjob?jk=2ec84c14bbe42215</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Wausau, WI, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Kafka, Snowflake, Oracle, ETL, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,94 +3331,94 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8bc2ea076a0ded7</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a4a5c971b6dae8</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Sr. Software Engineer, Enterprise Software</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee0fd3306ac2ce34</t>
+          <t>https://www.indeed.com/viewjob?jk=424a613517dace69</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Systems Administrator - Junior</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Alternative Information Systems</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93bbd1487e7d0fd7</t>
+          <t>https://www.indeed.com/viewjob?jk=87325485029af851</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Computer Data Engineering Intern/Co-Op</t>
+          <t>Analytics Developer, Enterprise Analytics (Data Shared Services)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>StandardAero</t>
+          <t>NewYork-Presbyterian Hospital</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Spark, SQL Server, PostgreSQL, MySQL, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, Power BI, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a982d1d82cbd60b</t>
+          <t>https://www.indeed.com/viewjob?jk=a889968da2ddc13e</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Sustainability Data and AI Consultant</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Plymouth, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, MLOps, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Git, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,172 +3471,172 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03c5058699b33f7</t>
+          <t>https://www.indeed.com/viewjob?jk=7976a31d4fb905fe</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Engineer - Long Beach, CA</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
+          <t>AWS, S3, Databricks, Kafka, Snowflake, PostgreSQL, Data Modeling, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e11fa47875d4b9f</t>
+          <t>https://www.indeed.com/viewjob?jk=0309d0101fc2195f</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Systems Administrator - Junior</t>
+          <t>Data Engineer (Business Intelligence) - Hybrid</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Alternative Information Systems</t>
+          <t>Blue Cross Blue Shield of Arizona</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>RDS, Hadoop, Scala, Snowflake, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87325485029af851</t>
+          <t>https://www.indeed.com/viewjob?jk=b876b640329d1da8</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>inversion</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=276c91b178e50bc3</t>
+          <t>https://www.indeed.com/viewjob?jk=5fdf01ee46ca5c04</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior .net Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Knowtion Health</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>S3, Azure, Data Factory, Scala, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ec84c14bbe42215</t>
+          <t>https://www.indeed.com/viewjob?jk=fe12ac26edf139f6</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer - Python/Agentic AI</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Wausau, WI, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, Snowflake, Oracle, ETL, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,67 +3646,67 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a4a5c971b6dae8</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2ba4e75ec79621</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Enterprise Software</t>
+          <t>Software Engineering Supervisor - Hybrid</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Sunrise Banks</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, NoSQL, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424a613517dace69</t>
+          <t>https://www.indeed.com/viewjob?jk=853197679fd8570c</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Analytics Developer, Enterprise Analytics (Data Shared Services)</t>
+          <t>Sr. Associate Software Engineer (Healthcare Data Integration)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>NewYork-Presbyterian Hospital</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, Power BI, Azure DevOps, Git</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a889968da2ddc13e</t>
+          <t>https://www.indeed.com/viewjob?jk=c5cc7c095dc341df</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Software Engineer III - Senior Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>AiPrise</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Terraform, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bfc9d48bb1fdefc</t>
+          <t>https://www.indeed.com/viewjob?jk=321ab7e09526522f</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sustainability Data and AI Consultant</t>
+          <t>Ruby on Rails Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ACA Group</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Git, Python</t>
+          <t>AWS, S3, ECS, RDS, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7976a31d4fb905fe</t>
+          <t>https://www.indeed.com/viewjob?jk=055ba32ff0f18bd8</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SecOps Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Midwest Tape</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>Holland, OH, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Kafka, Snowflake, PostgreSQL, Data Modeling, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,287 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0309d0101fc2195f</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Data Engineer (Business Intelligence) - Hybrid</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Blue Cross Blue Shield of Arizona</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Scala, Snowflake, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b876b640329d1da8</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>inversion</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5fdf01ee46ca5c04</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Knowtion Health</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>S3, Azure, Data Factory, Scala, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe12ac26edf139f6</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Python/Agentic AI</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>BlackLine</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Pleasanton, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2ba4e75ec79621</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>SecOps Engineer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Midwest Tape</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Holland, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=965702c6436d9964</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Software Engineering Supervisor - Hybrid</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Sunrise Banks</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Saint Paul, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, NoSQL, CI/CD, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=853197679fd8570c</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Sr. Associate Software Engineer (Healthcare Data Integration)</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>McKesson</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c5cc7c095dc341df</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Software Engineer III - Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>AiPrise</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Terraform, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=321ab7e09526522f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-26.xlsx
+++ b/results/job_matches_2026-06-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -561,29 +561,29 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171509f615b5daa2</t>
+          <t>https://www.indeed.com/viewjob?jk=0631739ce734e7c7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Manufacturing Intelligence, Machine Learning &amp; AI</t>
+          <t>Engineer/Sr Engineer, IT Data</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wa-Ni Village, TN, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ab95f94071e971b</t>
+          <t>https://www.indeed.com/viewjob?jk=171509f615b5daa2</t>
         </is>
       </c>
     </row>
@@ -678,25 +678,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior IT Big Data Developer</t>
+          <t>Mainframe Analyst (Healthcare)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>NSV IT SOLUTIONS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae26c12caca27959</t>
+          <t>https://www.indeed.com/viewjob?jk=529186dc1f0e5461</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer Senior - Big Data Platform Team</t>
+          <t>Senior IT Big Data Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Spark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bd359ddd135794e</t>
+          <t>https://www.indeed.com/viewjob?jk=ae26c12caca27959</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer</t>
+          <t>Data Engineer Senior - Big Data Platform Team</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>S3, RDS, Azure, Spark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb360d7f7dedcd5</t>
+          <t>https://www.indeed.com/viewjob?jk=0bd359ddd135794e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer - Hybrid/Durham,NC</t>
+          <t>Senior IT Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,69 +801,69 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85d13cad9b24073</t>
+          <t>https://www.indeed.com/viewjob?jk=efb360d7f7dedcd5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GCP Technical Specialist</t>
+          <t>Senior Software Engineer - Enterprise Data Services</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Wellmark Blue Cross and Blue Shield</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a829451037364106</t>
+          <t>https://www.indeed.com/viewjob?jk=96ed3a70f59cd7a0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Enterprise Data Services</t>
+          <t>Software Engineer III (US)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ed3a70f59cd7a0</t>
+          <t>https://www.indeed.com/viewjob?jk=d3f872ac99e6bd1a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer III (US)</t>
+          <t>Data Architect (173743)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3f872ac99e6bd1a</t>
+          <t>https://www.indeed.com/viewjob?jk=c9545b3f6e705f68</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Professional Services Consultant</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ba41961ffb1881c</t>
+          <t>https://www.indeed.com/viewjob?jk=861d82e3c9e267af</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Full-Stack Java Developer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,69 +1011,69 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, Kafka, PostgreSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=651520622efc1265</t>
+          <t>https://www.indeed.com/viewjob?jk=32c289c0954d3b83</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Robotics Data Engineer/Data Scientist</t>
+          <t>Full-Stack Java Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, Cassandra, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, Kafka, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d4e995adafbb96</t>
+          <t>https://www.indeed.com/viewjob?jk=651520622efc1265</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Coastal</t>
+          <t>Fubo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a700c4126f5f39e0</t>
+          <t>https://www.indeed.com/viewjob?jk=0e24be3cd83341f1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Robotics Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Arc Technologies Group</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, Cassandra, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,19 +1126,19 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ccc63169a66ef59</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d4e995adafbb96</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Remote Kubernetes Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cloud Data Vision</t>
+          <t>Coastal</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5be313cc3b61a58</t>
+          <t>https://www.indeed.com/viewjob?jk=a700c4126f5f39e0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>New York City Department of Sanitation</t>
+          <t>Arc Technologies Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Informatica PowerCenter, Oracle, Data Modeling, ETL, ELT, Pentaho</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f58c8be3a69d599b</t>
+          <t>https://www.indeed.com/viewjob?jk=8ccc63169a66ef59</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Remote Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Cloud Data Vision</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d54d860c68542f20</t>
+          <t>https://www.indeed.com/viewjob?jk=b5be313cc3b61a58</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Developer Operations Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Transcor Data Services</t>
+          <t>New York City Department of Sanitation</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Databricks, Spark, PySpark, Informatica PowerCenter, Oracle, Data Modeling, ETL, ELT, Pentaho</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b84e13a37c8822b9</t>
+          <t>https://www.indeed.com/viewjob?jk=f58c8be3a69d599b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Univision Communications Inc</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, Google Cloud Platform, GCP, Hadoop, Spark, Scala, dbt, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2f885fbfd483879</t>
+          <t>https://www.indeed.com/viewjob?jk=d54d860c68542f20</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer II - Global Servicing Technology</t>
+          <t>Developer Operations Engineer I</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Transcor Data Services</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c63a2ab17c26b27</t>
+          <t>https://www.indeed.com/viewjob?jk=b84e13a37c8822b9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer, League Analytics &amp; Infrastructure</t>
+          <t>Site Reliability Engineer – Oracle DB</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Major League Baseball</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e63e2ea97ff196b</t>
+          <t>https://www.indeed.com/viewjob?jk=caa3611b23da5c7d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MNTN</t>
+          <t>Univision Communications Inc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, Google Cloud Platform, GCP, Hadoop, Spark, Scala, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3610cfdfc0364b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=b2f885fbfd483879</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Data Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9a38e235659081</t>
+          <t>https://www.indeed.com/viewjob?jk=6c63a2ab17c26b27</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Senior Data Engineer - Orchestration</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Arvest Bank</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, GCP, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd0775a42f899524</t>
+          <t>https://www.indeed.com/viewjob?jk=e8fe7267b8b9de10</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Data Engineer, League Analytics &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Major League Baseball</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b33138f7850dfefc</t>
+          <t>https://www.indeed.com/viewjob?jk=5e63e2ea97ff196b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>MNTN</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a342726a84e27f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=3610cfdfc0364b8e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Senior Software Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c186d8b7ac65fdf8</t>
+          <t>https://www.indeed.com/viewjob?jk=6c3e33c47a701cd2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Senior Software Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95cc142f3e2617a6</t>
+          <t>https://www.indeed.com/viewjob?jk=03e620dabe0cd123</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Senior Software Engineer | Middleware</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>ExtraHop Networks</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, S3, SQS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db16f20add9ea986</t>
+          <t>https://www.indeed.com/viewjob?jk=111ecbafdd773723</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1382d06b80fb6867</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9a38e235659081</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcad5c4e643319ff</t>
+          <t>https://www.indeed.com/viewjob?jk=cd0775a42f899524</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e64526422d931b</t>
+          <t>https://www.indeed.com/viewjob?jk=b33138f7850dfefc</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d627fd3422104c</t>
+          <t>https://www.indeed.com/viewjob?jk=a342726a84e27f8e</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fab8211cf6bde1e0</t>
+          <t>https://www.indeed.com/viewjob?jk=c186d8b7ac65fdf8</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bab721c73d545f</t>
+          <t>https://www.indeed.com/viewjob?jk=95cc142f3e2617a6</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85a706af297ba804</t>
+          <t>https://www.indeed.com/viewjob?jk=db16f20add9ea986</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13401bc8d0f3279e</t>
+          <t>https://www.indeed.com/viewjob?jk=1382d06b80fb6867</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31032458d140d1ae</t>
+          <t>https://www.indeed.com/viewjob?jk=bcad5c4e643319ff</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=115cfe00112809d8</t>
+          <t>https://www.indeed.com/viewjob?jk=40e64526422d931b</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=031a5b8865d1f458</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d627fd3422104c</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65c6bb88e77fa7e3</t>
+          <t>https://www.indeed.com/viewjob?jk=fab8211cf6bde1e0</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0426526011ecf8ab</t>
+          <t>https://www.indeed.com/viewjob?jk=05bab721c73d545f</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2f4ae59bb2e76db</t>
+          <t>https://www.indeed.com/viewjob?jk=85a706af297ba804</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc596e52195e0933</t>
+          <t>https://www.indeed.com/viewjob?jk=13401bc8d0f3279e</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44f8b5180e01e140</t>
+          <t>https://www.indeed.com/viewjob?jk=31032458d140d1ae</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0b8f364ebc3247</t>
+          <t>https://www.indeed.com/viewjob?jk=115cfe00112809d8</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef9c01896959f630</t>
+          <t>https://www.indeed.com/viewjob?jk=031a5b8865d1f458</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271061dada6a961f</t>
+          <t>https://www.indeed.com/viewjob?jk=65c6bb88e77fa7e3</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1faf6e04fa2bbdcf</t>
+          <t>https://www.indeed.com/viewjob?jk=0426526011ecf8ab</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9794568eb039870</t>
+          <t>https://www.indeed.com/viewjob?jk=e2f4ae59bb2e76db</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1560887d7cb316fd</t>
+          <t>https://www.indeed.com/viewjob?jk=fc596e52195e0933</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd4ac5f09111b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=44f8b5180e01e140</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dee274917e4b9029</t>
+          <t>https://www.indeed.com/viewjob?jk=af0b8f364ebc3247</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c1f0804f082a435</t>
+          <t>https://www.indeed.com/viewjob?jk=ef9c01896959f630</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bcfef10dd24abe4</t>
+          <t>https://www.indeed.com/viewjob?jk=271061dada6a961f</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d3b83605c8a2df</t>
+          <t>https://www.indeed.com/viewjob?jk=1faf6e04fa2bbdcf</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=940dcb7683294d7b</t>
+          <t>https://www.indeed.com/viewjob?jk=f9794568eb039870</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbb60bebb7779e64</t>
+          <t>https://www.indeed.com/viewjob?jk=1560887d7cb316fd</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37d2114cee6dba4</t>
+          <t>https://www.indeed.com/viewjob?jk=bdd4ac5f09111b4e</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39c8b726cdb22aa</t>
+          <t>https://www.indeed.com/viewjob?jk=dee274917e4b9029</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd9a756aa23e011c</t>
+          <t>https://www.indeed.com/viewjob?jk=2c1f0804f082a435</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22d070dab1e1cb93</t>
+          <t>https://www.indeed.com/viewjob?jk=2bcfef10dd24abe4</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4045cf1c680be7b6</t>
+          <t>https://www.indeed.com/viewjob?jk=71d3b83605c8a2df</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f4daad7fda9ff7</t>
+          <t>https://www.indeed.com/viewjob?jk=940dcb7683294d7b</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0671107537ae859</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb60bebb7779e64</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a057a8d1dc27a54f</t>
+          <t>https://www.indeed.com/viewjob?jk=c37d2114cee6dba4</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec8eebe082d41ed</t>
+          <t>https://www.indeed.com/viewjob?jk=c39c8b726cdb22aa</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3912346602551520</t>
+          <t>https://www.indeed.com/viewjob?jk=bd9a756aa23e011c</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c6b2ae9b514e3c3</t>
+          <t>https://www.indeed.com/viewjob?jk=22d070dab1e1cb93</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdeb6923f62c2160</t>
+          <t>https://www.indeed.com/viewjob?jk=4045cf1c680be7b6</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8bc2ea076a0ded7</t>
+          <t>https://www.indeed.com/viewjob?jk=d5f4daad7fda9ff7</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee0fd3306ac2ce34</t>
+          <t>https://www.indeed.com/viewjob?jk=d0671107537ae859</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Plymouth, MI, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, MLOps, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,67 +3191,67 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03c5058699b33f7</t>
+          <t>https://www.indeed.com/viewjob?jk=a057a8d1dc27a54f</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Computer Data Engineering Intern/Co-Op</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>StandardAero</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Spark, SQL Server, PostgreSQL, MySQL, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a982d1d82cbd60b</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec8eebe082d41ed</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=276c91b178e50bc3</t>
+          <t>https://www.indeed.com/viewjob?jk=3912346602551520</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior .net Software Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ec84c14bbe42215</t>
+          <t>https://www.indeed.com/viewjob?jk=0c6b2ae9b514e3c3</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Wausau, WI, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, Snowflake, Oracle, ETL, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,67 +3331,67 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a4a5c971b6dae8</t>
+          <t>https://www.indeed.com/viewjob?jk=cdeb6923f62c2160</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Enterprise Software</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424a613517dace69</t>
+          <t>https://www.indeed.com/viewjob?jk=e8bc2ea076a0ded7</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Systems Administrator - Junior</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Alternative Information Systems</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87325485029af851</t>
+          <t>https://www.indeed.com/viewjob?jk=ee0fd3306ac2ce34</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Analytics Developer, Enterprise Analytics (Data Shared Services)</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>NewYork-Presbyterian Hospital</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Plymouth, MI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,42 +3426,42 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, Power BI, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, MLOps, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a889968da2ddc13e</t>
+          <t>https://www.indeed.com/viewjob?jk=f03c5058699b33f7</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sustainability Data and AI Consultant</t>
+          <t>Data Engineer - 2 Openings</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Blood Cancer United</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Git, Python</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, Scala, Snowflake, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,112 +3471,112 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7976a31d4fb905fe</t>
+          <t>https://www.indeed.com/viewjob?jk=dd9f154e39bab643</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Computer Data Engineering Intern/Co-Op</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>StandardAero</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Kafka, Snowflake, PostgreSQL, Data Modeling, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Hadoop, Spark, SQL Server, PostgreSQL, MySQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0309d0101fc2195f</t>
+          <t>https://www.indeed.com/viewjob?jk=4a982d1d82cbd60b</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer (Business Intelligence) - Hybrid</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Scala, Snowflake, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b876b640329d1da8</t>
+          <t>https://www.indeed.com/viewjob?jk=276c91b178e50bc3</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior .net Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>inversion</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fdf01ee46ca5c04</t>
+          <t>https://www.indeed.com/viewjob?jk=2ec84c14bbe42215</t>
         </is>
       </c>
     </row>
@@ -3588,117 +3588,117 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Knowtion Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wausau, WI, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>S3, Azure, Data Factory, Scala, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Kafka, Snowflake, Oracle, ETL, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe12ac26edf139f6</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a4a5c971b6dae8</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python/Agentic AI</t>
+          <t>Analytics Developer, Enterprise Analytics (Data Shared Services)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>NewYork-Presbyterian Hospital</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, Power BI, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2ba4e75ec79621</t>
+          <t>https://www.indeed.com/viewjob?jk=a889968da2ddc13e</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineering Supervisor - Hybrid</t>
+          <t>Sr. Software Engineer, Enterprise Software</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Sunrise Banks</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, NoSQL, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=853197679fd8570c</t>
+          <t>https://www.indeed.com/viewjob?jk=424a613517dace69</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr. Associate Software Engineer (Healthcare Data Integration)</t>
+          <t>Senior Data Infra Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Newsbreak</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
+          <t>AWS, Glue, EMR, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5cc7c095dc341df</t>
+          <t>https://www.indeed.com/viewjob?jk=0bce72fe2aabb677</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer III - Senior Engineer</t>
+          <t>Software Engineer ll, Data Platform</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>AiPrise</t>
+          <t>Cohere Health</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Terraform, Docker, Kubernetes, Python</t>
+          <t>AWS, EMR, Athena, S3, RDS, Scala, Kafka, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=321ab7e09526522f</t>
+          <t>https://www.indeed.com/viewjob?jk=80e694b601457a09</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Ruby on Rails Developer</t>
+          <t>Sustainability Data and AI Consultant</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ACA Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Git, Python</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=055ba32ff0f18bd8</t>
+          <t>https://www.indeed.com/viewjob?jk=7976a31d4fb905fe</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SecOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Midwest Tape</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Holland, OH, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,15 +3811,295 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
+          <t>AWS, S3, Databricks, Kafka, Snowflake, PostgreSQL, Data Modeling, Docker, Kubernetes, Airflow</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0309d0101fc2195f</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Data Engineer (Business Intelligence) - Hybrid</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Blue Cross Blue Shield of Arizona</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Scala, Snowflake, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b876b640329d1da8</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>inversion</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5fdf01ee46ca5c04</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Knowtion Health</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>S3, Azure, Data Factory, Scala, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe12ac26edf139f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Snowflake Architect</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Blaine, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=171a3405a6bf87d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Python/Agentic AI</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>BlackLine</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Pleasanton, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f2ba4e75ec79621</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Software Engineering Supervisor - Hybrid</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Sunrise Banks</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, NoSQL, CI/CD, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=853197679fd8570c</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Ruby on Rails Developer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>ACA Group</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, RDS, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=055ba32ff0f18bd8</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>SecOps Engineer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Midwest Tape</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Holland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
           <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=965702c6436d9964</t>
         </is>

--- a/results/job_matches_2026-06-26.xlsx
+++ b/results/job_matches_2026-06-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,52 +503,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Warehouse Engineer</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maverick Payments</t>
+          <t>Resmed</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, Kinesis, RDS, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9912f562ebafa77</t>
+          <t>https://www.indeed.com/viewjob?jk=db8f881d56beb45b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Edwards Lifesciences</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0631739ce734e7c7</t>
+          <t>https://www.indeed.com/viewjob?jk=02a96598db050be0</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -596,64 +596,64 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171509f615b5daa2</t>
+          <t>https://www.indeed.com/viewjob?jk=0631739ce734e7c7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Engineer/Sr Engineer, IT Data</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efacd6764e780443</t>
+          <t>https://www.indeed.com/viewjob?jk=171509f615b5daa2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>U.S. Financial Technology</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,29 +661,29 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a593e5a13bf91848</t>
+          <t>https://www.indeed.com/viewjob?jk=efacd6764e780443</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mainframe Analyst (Healthcare)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NSV IT SOLUTIONS</t>
+          <t>U.S. Financial Technology</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=529186dc1f0e5461</t>
+          <t>https://www.indeed.com/viewjob?jk=a593e5a13bf91848</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior IT Big Data Developer</t>
+          <t>Mainframe Analyst (Healthcare)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>NSV IT SOLUTIONS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae26c12caca27959</t>
+          <t>https://www.indeed.com/viewjob?jk=529186dc1f0e5461</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer Senior - Big Data Platform Team</t>
+          <t>Data Architect – Washington, DC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Spark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bd359ddd135794e</t>
+          <t>https://www.indeed.com/viewjob?jk=94d5786e7c110147</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer</t>
+          <t>Senior IT Big Data Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb360d7f7dedcd5</t>
+          <t>https://www.indeed.com/viewjob?jk=ae26c12caca27959</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Enterprise Data Services</t>
+          <t>Data Engineer Senior - Big Data Platform Team</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS</t>
+          <t>S3, RDS, Azure, Spark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ed3a70f59cd7a0</t>
+          <t>https://www.indeed.com/viewjob?jk=0bd359ddd135794e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer III (US)</t>
+          <t>Senior IT Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3f872ac99e6bd1a</t>
+          <t>https://www.indeed.com/viewjob?jk=efb360d7f7dedcd5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Architect (173743)</t>
+          <t>Senior Software Engineer - Enterprise Data Services</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Wellmark Blue Cross and Blue Shield</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala, Snowflake, Oracle</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9545b3f6e705f68</t>
+          <t>https://www.indeed.com/viewjob?jk=96ed3a70f59cd7a0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Consultant- Data/AI Due Diligence-MTS</t>
+          <t>Software Engineer III (US)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b6bc1ec4cda3c8e</t>
+          <t>https://www.indeed.com/viewjob?jk=d3f872ac99e6bd1a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Senior Consultant- Data/AI Due Diligence-MTS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861d82e3c9e267af</t>
+          <t>https://www.indeed.com/viewjob?jk=7b6bc1ec4cda3c8e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Architect (173743)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c289c0954d3b83</t>
+          <t>https://www.indeed.com/viewjob?jk=c9545b3f6e705f68</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Full-Stack Java Developer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, Kafka, PostgreSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=651520622efc1265</t>
+          <t>https://www.indeed.com/viewjob?jk=22692d347007686c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Engineering</t>
+          <t>Senior Engineer, Invest Tech</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fubo</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e24be3cd83341f1</t>
+          <t>https://www.indeed.com/viewjob?jk=418fe6804d9bbee5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Robotics Data Engineer/Data Scientist</t>
+          <t>Senior Engineer, Invest Tech</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, Cassandra, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d4e995adafbb96</t>
+          <t>https://www.indeed.com/viewjob?jk=455cbc0d06bec7dd</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Coastal</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a700c4126f5f39e0</t>
+          <t>https://www.indeed.com/viewjob?jk=861d82e3c9e267af</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Arc Technologies Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ccc63169a66ef59</t>
+          <t>https://www.indeed.com/viewjob?jk=32c289c0954d3b83</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Remote Kubernetes Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cloud Data Vision</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5be313cc3b61a58</t>
+          <t>https://www.indeed.com/viewjob?jk=563ad203b5a2853e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>New York City Department of Sanitation</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Informatica PowerCenter, Oracle, Data Modeling, ETL, ELT, Pentaho</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f58c8be3a69d599b</t>
+          <t>https://www.indeed.com/viewjob?jk=9c88857b2990a629</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d54d860c68542f20</t>
+          <t>https://www.indeed.com/viewjob?jk=6c30d6189ed53ff4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Developer Operations Engineer I</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Transcor Data Services</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b84e13a37c8822b9</t>
+          <t>https://www.indeed.com/viewjob?jk=c9f1090e8d875682</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer – Oracle DB</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caa3611b23da5c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=09009f7e617a8382</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Univision Communications Inc</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, Google Cloud Platform, GCP, Hadoop, Spark, Scala, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,242 +1406,242 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2f885fbfd483879</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c113a0ea31c0ed</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer II - Global Servicing Technology</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c63a2ab17c26b27</t>
+          <t>https://www.indeed.com/viewjob?jk=d5962eb966972f6e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Orchestration</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Arvest Bank</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8fe7267b8b9de10</t>
+          <t>https://www.indeed.com/viewjob?jk=b49f50dbf2988c82</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer, League Analytics &amp; Infrastructure</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Major League Baseball</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, dbt, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e63e2ea97ff196b</t>
+          <t>https://www.indeed.com/viewjob?jk=d75b791cf50c1184</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MNTN</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3610cfdfc0364b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=776060619ca92d8b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Hybrid</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c3e33c47a701cd2</t>
+          <t>https://www.indeed.com/viewjob?jk=2362abd894783c27</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Hybrid</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e620dabe0cd123</t>
+          <t>https://www.indeed.com/viewjob?jk=992a2c5f94075440</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer | Middleware</t>
+          <t>Software Engineer 2 - Full Stack</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ExtraHop Networks</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Terraform</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=111ecbafdd773723</t>
+          <t>https://www.indeed.com/viewjob?jk=69e822c1cf66e308</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Software Engineer 2 - Full Stack</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9a38e235659081</t>
+          <t>https://www.indeed.com/viewjob?jk=37dbcc8bf6973335</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Software Engineer 2 - Full Stack</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd0775a42f899524</t>
+          <t>https://www.indeed.com/viewjob?jk=d84fecedb12dd363</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Software Engineer 2 - Full Stack</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,67 +1756,67 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b33138f7850dfefc</t>
+          <t>https://www.indeed.com/viewjob?jk=abe999fc3b54fcb4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Full-Stack Java Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, Kafka, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a342726a84e27f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=651520622efc1265</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Fubo</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c186d8b7ac65fdf8</t>
+          <t>https://www.indeed.com/viewjob?jk=0e24be3cd83341f1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Senior Robotics Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, Cassandra, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95cc142f3e2617a6</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d4e995adafbb96</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Coastal</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db16f20add9ea986</t>
+          <t>https://www.indeed.com/viewjob?jk=a700c4126f5f39e0</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Data Platform Engineer (Associate)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1382d06b80fb6867</t>
+          <t>https://www.indeed.com/viewjob?jk=52b81f936f231329</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Arc Technologies Group</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcad5c4e643319ff</t>
+          <t>https://www.indeed.com/viewjob?jk=8ccc63169a66ef59</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Remote Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cloud Data Vision</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e64526422d931b</t>
+          <t>https://www.indeed.com/viewjob?jk=b5be313cc3b61a58</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>New York City Department of Sanitation</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Databricks, Spark, PySpark, Informatica PowerCenter, Oracle, Data Modeling, ETL, ELT, Pentaho</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d627fd3422104c</t>
+          <t>https://www.indeed.com/viewjob?jk=f58c8be3a69d599b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fab8211cf6bde1e0</t>
+          <t>https://www.indeed.com/viewjob?jk=d54d860c68542f20</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Developer Operations Engineer I</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Transcor Data Services</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bab721c73d545f</t>
+          <t>https://www.indeed.com/viewjob?jk=b84e13a37c8822b9</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Site Reliability Engineer – Oracle DB</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85a706af297ba804</t>
+          <t>https://www.indeed.com/viewjob?jk=caa3611b23da5c7d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Univision Communications Inc</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, IAM, Google Cloud Platform, GCP, Hadoop, Spark, Scala, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13401bc8d0f3279e</t>
+          <t>https://www.indeed.com/viewjob?jk=b2f885fbfd483879</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Senior Data Engineer - Orchestration</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Arvest Bank</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, GCP, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31032458d140d1ae</t>
+          <t>https://www.indeed.com/viewjob?jk=e8fe7267b8b9de10</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Data Engineer, League Analytics &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Major League Baseball</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=115cfe00112809d8</t>
+          <t>https://www.indeed.com/viewjob?jk=5e63e2ea97ff196b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>MNTN</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=031a5b8865d1f458</t>
+          <t>https://www.indeed.com/viewjob?jk=3610cfdfc0364b8e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Senior Software Engineer | Middleware</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>ExtraHop Networks</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, S3, SQS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65c6bb88e77fa7e3</t>
+          <t>https://www.indeed.com/viewjob?jk=111ecbafdd773723</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Senior Software Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0426526011ecf8ab</t>
+          <t>https://www.indeed.com/viewjob?jk=6c3e33c47a701cd2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Senior Software Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2f4ae59bb2e76db</t>
+          <t>https://www.indeed.com/viewjob?jk=03e620dabe0cd123</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc596e52195e0933</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9a38e235659081</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44f8b5180e01e140</t>
+          <t>https://www.indeed.com/viewjob?jk=cd0775a42f899524</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0b8f364ebc3247</t>
+          <t>https://www.indeed.com/viewjob?jk=b33138f7850dfefc</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef9c01896959f630</t>
+          <t>https://www.indeed.com/viewjob?jk=a342726a84e27f8e</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271061dada6a961f</t>
+          <t>https://www.indeed.com/viewjob?jk=c186d8b7ac65fdf8</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1faf6e04fa2bbdcf</t>
+          <t>https://www.indeed.com/viewjob?jk=95cc142f3e2617a6</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9794568eb039870</t>
+          <t>https://www.indeed.com/viewjob?jk=db16f20add9ea986</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1560887d7cb316fd</t>
+          <t>https://www.indeed.com/viewjob?jk=1382d06b80fb6867</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd4ac5f09111b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=bcad5c4e643319ff</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dee274917e4b9029</t>
+          <t>https://www.indeed.com/viewjob?jk=40e64526422d931b</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c1f0804f082a435</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d627fd3422104c</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bcfef10dd24abe4</t>
+          <t>https://www.indeed.com/viewjob?jk=fab8211cf6bde1e0</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d3b83605c8a2df</t>
+          <t>https://www.indeed.com/viewjob?jk=05bab721c73d545f</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=940dcb7683294d7b</t>
+          <t>https://www.indeed.com/viewjob?jk=85a706af297ba804</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbb60bebb7779e64</t>
+          <t>https://www.indeed.com/viewjob?jk=13401bc8d0f3279e</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37d2114cee6dba4</t>
+          <t>https://www.indeed.com/viewjob?jk=31032458d140d1ae</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39c8b726cdb22aa</t>
+          <t>https://www.indeed.com/viewjob?jk=115cfe00112809d8</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd9a756aa23e011c</t>
+          <t>https://www.indeed.com/viewjob?jk=031a5b8865d1f458</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22d070dab1e1cb93</t>
+          <t>https://www.indeed.com/viewjob?jk=65c6bb88e77fa7e3</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4045cf1c680be7b6</t>
+          <t>https://www.indeed.com/viewjob?jk=0426526011ecf8ab</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f4daad7fda9ff7</t>
+          <t>https://www.indeed.com/viewjob?jk=e2f4ae59bb2e76db</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0671107537ae859</t>
+          <t>https://www.indeed.com/viewjob?jk=fc596e52195e0933</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a057a8d1dc27a54f</t>
+          <t>https://www.indeed.com/viewjob?jk=44f8b5180e01e140</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec8eebe082d41ed</t>
+          <t>https://www.indeed.com/viewjob?jk=af0b8f364ebc3247</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3912346602551520</t>
+          <t>https://www.indeed.com/viewjob?jk=ef9c01896959f630</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c6b2ae9b514e3c3</t>
+          <t>https://www.indeed.com/viewjob?jk=271061dada6a961f</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdeb6923f62c2160</t>
+          <t>https://www.indeed.com/viewjob?jk=1faf6e04fa2bbdcf</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8bc2ea076a0ded7</t>
+          <t>https://www.indeed.com/viewjob?jk=f9794568eb039870</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee0fd3306ac2ce34</t>
+          <t>https://www.indeed.com/viewjob?jk=1560887d7cb316fd</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Plymouth, MI, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, MLOps, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03c5058699b33f7</t>
+          <t>https://www.indeed.com/viewjob?jk=bdd4ac5f09111b4e</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer - 2 Openings</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Blood Cancer United</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, Scala, Snowflake, Data Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,67 +3471,67 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd9f154e39bab643</t>
+          <t>https://www.indeed.com/viewjob?jk=dee274917e4b9029</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Computer Data Engineering Intern/Co-Op</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>StandardAero</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Spark, SQL Server, PostgreSQL, MySQL, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a982d1d82cbd60b</t>
+          <t>https://www.indeed.com/viewjob?jk=2c1f0804f082a435</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=276c91b178e50bc3</t>
+          <t>https://www.indeed.com/viewjob?jk=2bcfef10dd24abe4</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior .net Software Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ec84c14bbe42215</t>
+          <t>https://www.indeed.com/viewjob?jk=71d3b83605c8a2df</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Wausau, WI, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, Snowflake, Oracle, ETL, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,137 +3611,137 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a4a5c971b6dae8</t>
+          <t>https://www.indeed.com/viewjob?jk=940dcb7683294d7b</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Analytics Developer, Enterprise Analytics (Data Shared Services)</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>NewYork-Presbyterian Hospital</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, Power BI, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a889968da2ddc13e</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb60bebb7779e64</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Enterprise Software</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424a613517dace69</t>
+          <t>https://www.indeed.com/viewjob?jk=c37d2114cee6dba4</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Infra Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Newsbreak</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bce72fe2aabb677</t>
+          <t>https://www.indeed.com/viewjob?jk=c39c8b726cdb22aa</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer ll, Data Platform</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Cohere Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, S3, RDS, Scala, Kafka, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e694b601457a09</t>
+          <t>https://www.indeed.com/viewjob?jk=bd9a756aa23e011c</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sustainability Data and AI Consultant</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Git, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7976a31d4fb905fe</t>
+          <t>https://www.indeed.com/viewjob?jk=22d070dab1e1cb93</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Kafka, Snowflake, PostgreSQL, Data Modeling, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,137 +3821,137 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0309d0101fc2195f</t>
+          <t>https://www.indeed.com/viewjob?jk=4045cf1c680be7b6</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer (Business Intelligence) - Hybrid</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Scala, Snowflake, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b876b640329d1da8</t>
+          <t>https://www.indeed.com/viewjob?jk=d5f4daad7fda9ff7</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>inversion</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fdf01ee46ca5c04</t>
+          <t>https://www.indeed.com/viewjob?jk=d0671107537ae859</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Knowtion Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>S3, Azure, Data Factory, Scala, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe12ac26edf139f6</t>
+          <t>https://www.indeed.com/viewjob?jk=a057a8d1dc27a54f</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171a3405a6bf87d5</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec8eebe082d41ed</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python/Agentic AI</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2ba4e75ec79621</t>
+          <t>https://www.indeed.com/viewjob?jk=3912346602551520</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Engineering Supervisor - Hybrid</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Sunrise Banks</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, NoSQL, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=853197679fd8570c</t>
+          <t>https://www.indeed.com/viewjob?jk=0c6b2ae9b514e3c3</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Ruby on Rails Developer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ACA Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,42 +4066,847 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=055ba32ff0f18bd8</t>
+          <t>https://www.indeed.com/viewjob?jk=cdeb6923f62c2160</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SecOps Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Midwest Tape</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Holland, OH, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e8bc2ea076a0ded7</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Software Engineer - Search and Personalization</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>MT, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee0fd3306ac2ce34</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Senior Big Data Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a57c804e0f6cdd8d</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Senior AI Software Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Bosch</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Plymouth, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, MLOps, CI/CD, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f03c5058699b33f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Data Engineer - 2 Openings</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Blood Cancer United</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, Scala, Snowflake, Data Modeling, Kimball</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd9f154e39bab643</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Computer Data Engineering Intern/Co-Op</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>StandardAero</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Hadoop, Spark, SQL Server, PostgreSQL, MySQL, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a982d1d82cbd60b</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Minnetonka, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=276c91b178e50bc3</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Analytics Developer, Enterprise Analytics (Data Shared Services)</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>NewYork-Presbyterian Hospital</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Manhattan, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, Power BI, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a889968da2ddc13e</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Senior .net Software Engineer</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ec84c14bbe42215</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Wausau, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Kafka, Snowflake, Oracle, ETL, CI/CD, Jenkins, Jenkins, Airflow</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f2a4a5c971b6dae8</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer, Enterprise Software</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Rivian</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=424a613517dace69</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>MuleSoft QA Engineer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>UniFirst</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Wilmington, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
         <v>10.4</v>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=965702c6436d9964</t>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ec42b333047dabf</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Senior Data Infra Engineer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Newsbreak</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0bce72fe2aabb677</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Sustainability Data and AI Consultant</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc927e4fc5649b27</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Software Engineer ll, Data Platform</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Cohere Health</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, EMR, Athena, S3, RDS, Scala, Kafka, dbt, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80e694b601457a09</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Sustainability Data and AI Consultant</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7976a31d4fb905fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Lake Buena Vista, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, S3, Databricks, Kafka, Snowflake, PostgreSQL, Data Modeling, Docker, Kubernetes, Airflow</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0309d0101fc2195f</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Data Engineer (Business Intelligence) - Hybrid</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Blue Cross Blue Shield of Arizona</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Scala, Snowflake, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b876b640329d1da8</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Knowtion Health</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>S3, Azure, Data Factory, Scala, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe12ac26edf139f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>MuleSoft Developer</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>UniFirst</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Wilmington, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2aedb694782bdb77</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Digital Services Engineer</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Continental</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Clinton, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, Docker, Kubernetes, Git, Python</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92b28fa10f3665b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Snowflake Architect</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Blaine, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=171a3405a6bf87d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Software Engineering Supervisor - Hybrid</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Sunrise Banks</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, NoSQL, CI/CD, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=853197679fd8570c</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Python/Agentic AI</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>BlackLine</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Pleasanton, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f2ba4e75ec79621</t>
         </is>
       </c>
     </row>
